--- a/artfynd/A 57918-2024 artfynd.xlsx
+++ b/artfynd/A 57918-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,6 +911,3651 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122083878</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57365</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Gåstjärnvalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>418620</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7053685</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122083897</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57365</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Gåstjärnvalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>418829</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7053675</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122083903</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57365</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Gåstjärnvalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>418664</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7053400</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>122083887</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57365</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Gåstjärnvalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>418757</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7053896</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>122083871</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57365</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Gåstjärnvalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>418491</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7053452</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122083881</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57365</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Gåstjärnvalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>418710</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7053790</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>122083899</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57365</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Gåstjärnvalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>418744</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7053595</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>122083883</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57365</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Gåstjärnvalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>418739</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7053883</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>122083869</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57365</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Gåstjärnvalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>418453</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7053383</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>122083885</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57365</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Gåstjärnvalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>418741</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7053893</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>122083876</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57365</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Gåstjärnvalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>418613</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7053668</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>122083882</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57365</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Gåstjärnvalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>418746</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7053865</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>122083893</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57365</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Gåstjärnvalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>418775</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7053757</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>122083902</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57365</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Gåstjärnvalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>418725</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7053592</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>122083896</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57365</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Gåstjärnvalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>418900</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7053621</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>122083874</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57365</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Gåstjärnvalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>418592</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7053670</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>122083890</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57365</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Gåstjärnvalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>418789</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7053838</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>122083898</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57365</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Gåstjärnvalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>418731</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7053619</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>122083889</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57365</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Gåstjärnvalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>418787</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7053837</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>122083875</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57365</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Gåstjärnvalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>418602</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7053668</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>122083868</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57365</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Gåstjärnvalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>418309</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7053279</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>122083894</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57365</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Gåstjärnvalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>418782</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7053729</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>122083877</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57365</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Gåstjärnvalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>418615</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7053683</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>122083891</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57365</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Gåstjärnvalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>418789</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7053772</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>122083879</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57365</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Gåstjärnvalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>418631</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7053701</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>122083873</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57365</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Gåstjärnvalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>418544</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7053546</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>122083888</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57365</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Gåstjärnvalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>418785</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7053838</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>122083895</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57365</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Gåstjärnvalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>418939</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7053794</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>122083901</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57365</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Gåstjärnvalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>418735</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7053591</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>122083880</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57365</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Gåstjärnvalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>418705</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7053783</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>122083886</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57365</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Gåstjärnvalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>418755</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7053901</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>122083892</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57365</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Gåstjärnvalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>418769</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7053764</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>122083904</v>
+      </c>
+      <c r="B36" t="n">
+        <v>78629</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Gåstjärnvalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>418450</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7053262</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>riktigt</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>122083870</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57365</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Gåstjärnvalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>418476</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7053445</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 57918-2024 artfynd.xlsx
+++ b/artfynd/A 57918-2024 artfynd.xlsx
@@ -913,7 +913,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122083878</v>
+        <v>122083893</v>
       </c>
       <c r="B4" t="n">
         <v>57365</v>
@@ -953,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>418620</v>
+        <v>418775</v>
       </c>
       <c r="R4" t="n">
-        <v>7053685</v>
+        <v>7053757</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,7 +1020,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122083897</v>
+        <v>122083874</v>
       </c>
       <c r="B5" t="n">
         <v>57365</v>
@@ -1060,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>418829</v>
+        <v>418592</v>
       </c>
       <c r="R5" t="n">
-        <v>7053675</v>
+        <v>7053670</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,7 +1127,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122083903</v>
+        <v>122083892</v>
       </c>
       <c r="B6" t="n">
         <v>57365</v>
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>418664</v>
+        <v>418769</v>
       </c>
       <c r="R6" t="n">
-        <v>7053400</v>
+        <v>7053764</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1234,7 +1234,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122083887</v>
+        <v>122083882</v>
       </c>
       <c r="B7" t="n">
         <v>57365</v>
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>418757</v>
+        <v>418746</v>
       </c>
       <c r="R7" t="n">
-        <v>7053896</v>
+        <v>7053865</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122083871</v>
+        <v>122083904</v>
       </c>
       <c r="B8" t="n">
-        <v>57365</v>
+        <v>78631</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,21 +1357,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>418491</v>
+        <v>418450</v>
       </c>
       <c r="R8" t="n">
-        <v>7053452</v>
+        <v>7053262</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>riktigt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1448,7 +1448,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122083881</v>
+        <v>122083896</v>
       </c>
       <c r="B9" t="n">
         <v>57365</v>
@@ -1488,10 +1488,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>418710</v>
+        <v>418900</v>
       </c>
       <c r="R9" t="n">
-        <v>7053790</v>
+        <v>7053621</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1555,7 +1555,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122083899</v>
+        <v>122083886</v>
       </c>
       <c r="B10" t="n">
         <v>57365</v>
@@ -1595,10 +1595,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>418744</v>
+        <v>418755</v>
       </c>
       <c r="R10" t="n">
-        <v>7053595</v>
+        <v>7053901</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1662,7 +1662,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122083883</v>
+        <v>122083871</v>
       </c>
       <c r="B11" t="n">
         <v>57365</v>
@@ -1702,10 +1702,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>418739</v>
+        <v>418491</v>
       </c>
       <c r="R11" t="n">
-        <v>7053883</v>
+        <v>7053452</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1769,7 +1769,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122083869</v>
+        <v>122083895</v>
       </c>
       <c r="B12" t="n">
         <v>57365</v>
@@ -1803,28 +1803,16 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Gåstjärnvalen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>418453</v>
+        <v>418939</v>
       </c>
       <c r="R12" t="n">
-        <v>7053383</v>
+        <v>7053794</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1857,6 +1845,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1883,7 +1876,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122083885</v>
+        <v>122083877</v>
       </c>
       <c r="B13" t="n">
         <v>57365</v>
@@ -1923,10 +1916,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>418741</v>
+        <v>418615</v>
       </c>
       <c r="R13" t="n">
-        <v>7053893</v>
+        <v>7053683</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1963,7 +1956,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1990,7 +1983,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122083876</v>
+        <v>122083881</v>
       </c>
       <c r="B14" t="n">
         <v>57365</v>
@@ -2030,10 +2023,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>418613</v>
+        <v>418710</v>
       </c>
       <c r="R14" t="n">
-        <v>7053668</v>
+        <v>7053790</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2070,7 +2063,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2097,7 +2090,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122083882</v>
+        <v>122083888</v>
       </c>
       <c r="B15" t="n">
         <v>57365</v>
@@ -2137,10 +2130,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>418746</v>
+        <v>418785</v>
       </c>
       <c r="R15" t="n">
-        <v>7053865</v>
+        <v>7053838</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2177,7 +2170,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2204,7 +2197,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122083893</v>
+        <v>122083902</v>
       </c>
       <c r="B16" t="n">
         <v>57365</v>
@@ -2244,10 +2237,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>418775</v>
+        <v>418725</v>
       </c>
       <c r="R16" t="n">
-        <v>7053757</v>
+        <v>7053592</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2311,7 +2304,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122083902</v>
+        <v>122083873</v>
       </c>
       <c r="B17" t="n">
         <v>57365</v>
@@ -2351,10 +2344,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>418725</v>
+        <v>418544</v>
       </c>
       <c r="R17" t="n">
-        <v>7053592</v>
+        <v>7053546</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2418,7 +2411,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122083896</v>
+        <v>122083885</v>
       </c>
       <c r="B18" t="n">
         <v>57365</v>
@@ -2458,10 +2451,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>418900</v>
+        <v>418741</v>
       </c>
       <c r="R18" t="n">
-        <v>7053621</v>
+        <v>7053893</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2525,7 +2518,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122083874</v>
+        <v>122083890</v>
       </c>
       <c r="B19" t="n">
         <v>57365</v>
@@ -2565,10 +2558,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>418592</v>
+        <v>418789</v>
       </c>
       <c r="R19" t="n">
-        <v>7053670</v>
+        <v>7053838</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2605,7 +2598,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2632,7 +2625,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122083890</v>
+        <v>122083868</v>
       </c>
       <c r="B20" t="n">
         <v>57365</v>
@@ -2672,10 +2665,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>418789</v>
+        <v>418309</v>
       </c>
       <c r="R20" t="n">
-        <v>7053838</v>
+        <v>7053279</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2739,7 +2732,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122083898</v>
+        <v>122083876</v>
       </c>
       <c r="B21" t="n">
         <v>57365</v>
@@ -2779,10 +2772,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>418731</v>
+        <v>418613</v>
       </c>
       <c r="R21" t="n">
-        <v>7053619</v>
+        <v>7053668</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2819,7 +2812,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2846,7 +2839,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122083889</v>
+        <v>122083899</v>
       </c>
       <c r="B22" t="n">
         <v>57365</v>
@@ -2886,10 +2879,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>418787</v>
+        <v>418744</v>
       </c>
       <c r="R22" t="n">
-        <v>7053837</v>
+        <v>7053595</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2953,7 +2946,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122083875</v>
+        <v>122083884</v>
       </c>
       <c r="B23" t="n">
         <v>57365</v>
@@ -2993,10 +2986,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>418602</v>
+        <v>418739</v>
       </c>
       <c r="R23" t="n">
-        <v>7053668</v>
+        <v>7053883</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3060,7 +3053,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122083868</v>
+        <v>122083869</v>
       </c>
       <c r="B24" t="n">
         <v>57365</v>
@@ -3094,16 +3087,28 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Gåstjärnvalen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>418309</v>
+        <v>418453</v>
       </c>
       <c r="R24" t="n">
-        <v>7053279</v>
+        <v>7053383</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3136,11 +3141,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-01-10</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3167,7 +3167,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122083894</v>
+        <v>122083889</v>
       </c>
       <c r="B25" t="n">
         <v>57365</v>
@@ -3207,10 +3207,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>418782</v>
+        <v>418787</v>
       </c>
       <c r="R25" t="n">
-        <v>7053729</v>
+        <v>7053837</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3274,7 +3274,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122083877</v>
+        <v>122083898</v>
       </c>
       <c r="B26" t="n">
         <v>57365</v>
@@ -3314,10 +3314,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>418615</v>
+        <v>418731</v>
       </c>
       <c r="R26" t="n">
-        <v>7053683</v>
+        <v>7053619</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3381,7 +3381,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122083891</v>
+        <v>122083880</v>
       </c>
       <c r="B27" t="n">
         <v>57365</v>
@@ -3421,10 +3421,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>418789</v>
+        <v>418705</v>
       </c>
       <c r="R27" t="n">
-        <v>7053772</v>
+        <v>7053783</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3461,7 +3461,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3488,7 +3488,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122083879</v>
+        <v>122083891</v>
       </c>
       <c r="B28" t="n">
         <v>57365</v>
@@ -3528,10 +3528,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>418631</v>
+        <v>418789</v>
       </c>
       <c r="R28" t="n">
-        <v>7053701</v>
+        <v>7053772</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3568,7 +3568,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3595,7 +3595,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122083873</v>
+        <v>122083897</v>
       </c>
       <c r="B29" t="n">
         <v>57365</v>
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>418544</v>
+        <v>418829</v>
       </c>
       <c r="R29" t="n">
-        <v>7053546</v>
+        <v>7053675</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3702,7 +3702,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122083888</v>
+        <v>122083887</v>
       </c>
       <c r="B30" t="n">
         <v>57365</v>
@@ -3742,10 +3742,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>418785</v>
+        <v>418757</v>
       </c>
       <c r="R30" t="n">
-        <v>7053838</v>
+        <v>7053896</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3782,7 +3782,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3809,7 +3809,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122083895</v>
+        <v>122083879</v>
       </c>
       <c r="B31" t="n">
         <v>57365</v>
@@ -3849,10 +3849,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>418939</v>
+        <v>418631</v>
       </c>
       <c r="R31" t="n">
-        <v>7053794</v>
+        <v>7053701</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3916,7 +3916,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122083901</v>
+        <v>122083903</v>
       </c>
       <c r="B32" t="n">
         <v>57365</v>
@@ -3956,10 +3956,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>418735</v>
+        <v>418664</v>
       </c>
       <c r="R32" t="n">
-        <v>7053591</v>
+        <v>7053400</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3996,7 +3996,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4023,7 +4023,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122083880</v>
+        <v>122083878</v>
       </c>
       <c r="B33" t="n">
         <v>57365</v>
@@ -4063,10 +4063,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>418705</v>
+        <v>418620</v>
       </c>
       <c r="R33" t="n">
-        <v>7053783</v>
+        <v>7053685</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4130,7 +4130,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122083886</v>
+        <v>122083870</v>
       </c>
       <c r="B34" t="n">
         <v>57365</v>
@@ -4170,10 +4170,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>418755</v>
+        <v>418476</v>
       </c>
       <c r="R34" t="n">
-        <v>7053901</v>
+        <v>7053445</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4237,7 +4237,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122083892</v>
+        <v>122083894</v>
       </c>
       <c r="B35" t="n">
         <v>57365</v>
@@ -4277,10 +4277,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>418769</v>
+        <v>418782</v>
       </c>
       <c r="R35" t="n">
-        <v>7053764</v>
+        <v>7053729</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4317,7 +4317,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4344,10 +4344,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122083904</v>
+        <v>122083901</v>
       </c>
       <c r="B36" t="n">
-        <v>78629</v>
+        <v>57365</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4360,21 +4360,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4384,10 +4384,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>418450</v>
+        <v>418735</v>
       </c>
       <c r="R36" t="n">
-        <v>7053262</v>
+        <v>7053591</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4424,7 +4424,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>riktigt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4451,7 +4451,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122083870</v>
+        <v>122083875</v>
       </c>
       <c r="B37" t="n">
         <v>57365</v>
@@ -4491,10 +4491,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>418476</v>
+        <v>418602</v>
       </c>
       <c r="R37" t="n">
-        <v>7053445</v>
+        <v>7053668</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>

--- a/artfynd/A 57918-2024 artfynd.xlsx
+++ b/artfynd/A 57918-2024 artfynd.xlsx
@@ -913,7 +913,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122083893</v>
+        <v>122083902</v>
       </c>
       <c r="B4" t="n">
         <v>57365</v>
@@ -953,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>418775</v>
+        <v>418725</v>
       </c>
       <c r="R4" t="n">
-        <v>7053757</v>
+        <v>7053592</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,7 +1020,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122083874</v>
+        <v>122083877</v>
       </c>
       <c r="B5" t="n">
         <v>57365</v>
@@ -1060,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>418592</v>
+        <v>418615</v>
       </c>
       <c r="R5" t="n">
-        <v>7053670</v>
+        <v>7053683</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,7 +1127,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122083892</v>
+        <v>122083875</v>
       </c>
       <c r="B6" t="n">
         <v>57365</v>
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>418769</v>
+        <v>418602</v>
       </c>
       <c r="R6" t="n">
-        <v>7053764</v>
+        <v>7053668</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1234,7 +1234,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122083882</v>
+        <v>122083889</v>
       </c>
       <c r="B7" t="n">
         <v>57365</v>
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>418746</v>
+        <v>418787</v>
       </c>
       <c r="R7" t="n">
-        <v>7053865</v>
+        <v>7053837</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122083904</v>
+        <v>122083868</v>
       </c>
       <c r="B8" t="n">
-        <v>78631</v>
+        <v>57365</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,21 +1357,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>418450</v>
+        <v>418309</v>
       </c>
       <c r="R8" t="n">
-        <v>7053262</v>
+        <v>7053279</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>riktigt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1448,7 +1448,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122083896</v>
+        <v>122083894</v>
       </c>
       <c r="B9" t="n">
         <v>57365</v>
@@ -1488,10 +1488,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>418900</v>
+        <v>418782</v>
       </c>
       <c r="R9" t="n">
-        <v>7053621</v>
+        <v>7053729</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1555,7 +1555,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122083886</v>
+        <v>122083896</v>
       </c>
       <c r="B10" t="n">
         <v>57365</v>
@@ -1595,10 +1595,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>418755</v>
+        <v>418900</v>
       </c>
       <c r="R10" t="n">
-        <v>7053901</v>
+        <v>7053621</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1662,7 +1662,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122083871</v>
+        <v>122083883</v>
       </c>
       <c r="B11" t="n">
         <v>57365</v>
@@ -1702,10 +1702,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>418491</v>
+        <v>418739</v>
       </c>
       <c r="R11" t="n">
-        <v>7053452</v>
+        <v>7053883</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1769,7 +1769,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122083895</v>
+        <v>122083892</v>
       </c>
       <c r="B12" t="n">
         <v>57365</v>
@@ -1809,10 +1809,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>418939</v>
+        <v>418769</v>
       </c>
       <c r="R12" t="n">
-        <v>7053794</v>
+        <v>7053764</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1876,7 +1876,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122083877</v>
+        <v>122083898</v>
       </c>
       <c r="B13" t="n">
         <v>57365</v>
@@ -1916,10 +1916,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>418615</v>
+        <v>418731</v>
       </c>
       <c r="R13" t="n">
-        <v>7053683</v>
+        <v>7053619</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1983,10 +1983,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122083881</v>
+        <v>122083904</v>
       </c>
       <c r="B14" t="n">
-        <v>57365</v>
+        <v>78632</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1999,21 +1999,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2023,10 +2023,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>418710</v>
+        <v>418450</v>
       </c>
       <c r="R14" t="n">
-        <v>7053790</v>
+        <v>7053262</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>riktigt</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2090,7 +2090,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122083888</v>
+        <v>122083878</v>
       </c>
       <c r="B15" t="n">
         <v>57365</v>
@@ -2130,10 +2130,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>418785</v>
+        <v>418620</v>
       </c>
       <c r="R15" t="n">
-        <v>7053838</v>
+        <v>7053685</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2197,7 +2197,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122083902</v>
+        <v>122083886</v>
       </c>
       <c r="B16" t="n">
         <v>57365</v>
@@ -2237,10 +2237,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>418725</v>
+        <v>418755</v>
       </c>
       <c r="R16" t="n">
-        <v>7053592</v>
+        <v>7053901</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2304,7 +2304,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122083873</v>
+        <v>122083903</v>
       </c>
       <c r="B17" t="n">
         <v>57365</v>
@@ -2344,10 +2344,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>418544</v>
+        <v>418664</v>
       </c>
       <c r="R17" t="n">
-        <v>7053546</v>
+        <v>7053400</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2411,7 +2411,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122083885</v>
+        <v>122083890</v>
       </c>
       <c r="B18" t="n">
         <v>57365</v>
@@ -2451,10 +2451,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>418741</v>
+        <v>418789</v>
       </c>
       <c r="R18" t="n">
-        <v>7053893</v>
+        <v>7053838</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2518,7 +2518,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122083890</v>
+        <v>122083888</v>
       </c>
       <c r="B19" t="n">
         <v>57365</v>
@@ -2558,7 +2558,7 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>418789</v>
+        <v>418785</v>
       </c>
       <c r="R19" t="n">
         <v>7053838</v>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2625,7 +2625,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122083868</v>
+        <v>122083880</v>
       </c>
       <c r="B20" t="n">
         <v>57365</v>
@@ -2665,10 +2665,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>418309</v>
+        <v>418705</v>
       </c>
       <c r="R20" t="n">
-        <v>7053279</v>
+        <v>7053783</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2732,7 +2732,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122083876</v>
+        <v>122083871</v>
       </c>
       <c r="B21" t="n">
         <v>57365</v>
@@ -2772,10 +2772,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>418613</v>
+        <v>418491</v>
       </c>
       <c r="R21" t="n">
-        <v>7053668</v>
+        <v>7053452</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2812,7 +2812,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2839,7 +2839,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122083899</v>
+        <v>122083874</v>
       </c>
       <c r="B22" t="n">
         <v>57365</v>
@@ -2879,10 +2879,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>418744</v>
+        <v>418592</v>
       </c>
       <c r="R22" t="n">
-        <v>7053595</v>
+        <v>7053670</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2919,7 +2919,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2946,7 +2946,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122083884</v>
+        <v>122083876</v>
       </c>
       <c r="B23" t="n">
         <v>57365</v>
@@ -2986,10 +2986,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>418739</v>
+        <v>418613</v>
       </c>
       <c r="R23" t="n">
-        <v>7053883</v>
+        <v>7053668</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3026,7 +3026,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3053,7 +3053,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122083869</v>
+        <v>122083873</v>
       </c>
       <c r="B24" t="n">
         <v>57365</v>
@@ -3087,28 +3087,16 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Gåstjärnvalen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>418453</v>
+        <v>418544</v>
       </c>
       <c r="R24" t="n">
-        <v>7053383</v>
+        <v>7053546</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3141,6 +3129,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3167,7 +3160,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122083889</v>
+        <v>122083869</v>
       </c>
       <c r="B25" t="n">
         <v>57365</v>
@@ -3201,16 +3194,28 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Gåstjärnvalen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>418787</v>
+        <v>418453</v>
       </c>
       <c r="R25" t="n">
-        <v>7053837</v>
+        <v>7053383</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3243,11 +3248,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-01-10</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3274,7 +3274,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122083898</v>
+        <v>122083897</v>
       </c>
       <c r="B26" t="n">
         <v>57365</v>
@@ -3314,10 +3314,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>418731</v>
+        <v>418829</v>
       </c>
       <c r="R26" t="n">
-        <v>7053619</v>
+        <v>7053675</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3381,7 +3381,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122083880</v>
+        <v>122083887</v>
       </c>
       <c r="B27" t="n">
         <v>57365</v>
@@ -3421,10 +3421,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>418705</v>
+        <v>418757</v>
       </c>
       <c r="R27" t="n">
-        <v>7053783</v>
+        <v>7053896</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3488,7 +3488,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122083891</v>
+        <v>122083882</v>
       </c>
       <c r="B28" t="n">
         <v>57365</v>
@@ -3528,10 +3528,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>418789</v>
+        <v>418746</v>
       </c>
       <c r="R28" t="n">
-        <v>7053772</v>
+        <v>7053865</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3568,7 +3568,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3595,7 +3595,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122083897</v>
+        <v>122083879</v>
       </c>
       <c r="B29" t="n">
         <v>57365</v>
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>418829</v>
+        <v>418631</v>
       </c>
       <c r="R29" t="n">
-        <v>7053675</v>
+        <v>7053701</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3702,7 +3702,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122083887</v>
+        <v>122083885</v>
       </c>
       <c r="B30" t="n">
         <v>57365</v>
@@ -3742,10 +3742,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>418757</v>
+        <v>418741</v>
       </c>
       <c r="R30" t="n">
-        <v>7053896</v>
+        <v>7053893</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3782,7 +3782,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3809,7 +3809,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122083879</v>
+        <v>122083870</v>
       </c>
       <c r="B31" t="n">
         <v>57365</v>
@@ -3849,10 +3849,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>418631</v>
+        <v>418476</v>
       </c>
       <c r="R31" t="n">
-        <v>7053701</v>
+        <v>7053445</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3916,7 +3916,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122083903</v>
+        <v>122083895</v>
       </c>
       <c r="B32" t="n">
         <v>57365</v>
@@ -3956,10 +3956,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>418664</v>
+        <v>418939</v>
       </c>
       <c r="R32" t="n">
-        <v>7053400</v>
+        <v>7053794</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4023,7 +4023,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122083878</v>
+        <v>122083901</v>
       </c>
       <c r="B33" t="n">
         <v>57365</v>
@@ -4063,10 +4063,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>418620</v>
+        <v>418735</v>
       </c>
       <c r="R33" t="n">
-        <v>7053685</v>
+        <v>7053591</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4130,7 +4130,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122083870</v>
+        <v>122083893</v>
       </c>
       <c r="B34" t="n">
         <v>57365</v>
@@ -4170,10 +4170,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>418476</v>
+        <v>418775</v>
       </c>
       <c r="R34" t="n">
-        <v>7053445</v>
+        <v>7053757</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4237,7 +4237,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122083894</v>
+        <v>122083899</v>
       </c>
       <c r="B35" t="n">
         <v>57365</v>
@@ -4277,10 +4277,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>418782</v>
+        <v>418744</v>
       </c>
       <c r="R35" t="n">
-        <v>7053729</v>
+        <v>7053595</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4317,7 +4317,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4344,7 +4344,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122083901</v>
+        <v>122083881</v>
       </c>
       <c r="B36" t="n">
         <v>57365</v>
@@ -4384,10 +4384,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>418735</v>
+        <v>418710</v>
       </c>
       <c r="R36" t="n">
-        <v>7053591</v>
+        <v>7053790</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4424,7 +4424,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4451,7 +4451,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122083875</v>
+        <v>122083891</v>
       </c>
       <c r="B37" t="n">
         <v>57365</v>
@@ -4491,10 +4491,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>418602</v>
+        <v>418789</v>
       </c>
       <c r="R37" t="n">
-        <v>7053668</v>
+        <v>7053772</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 57918-2024 artfynd.xlsx
+++ b/artfynd/A 57918-2024 artfynd.xlsx
@@ -2411,7 +2411,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122083890</v>
+        <v>122083888</v>
       </c>
       <c r="B18" t="n">
         <v>57365</v>
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>418789</v>
+        <v>418785</v>
       </c>
       <c r="R18" t="n">
         <v>7053838</v>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2518,7 +2518,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122083888</v>
+        <v>122083890</v>
       </c>
       <c r="B19" t="n">
         <v>57365</v>
@@ -2558,7 +2558,7 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>418785</v>
+        <v>418789</v>
       </c>
       <c r="R19" t="n">
         <v>7053838</v>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 57918-2024 artfynd.xlsx
+++ b/artfynd/A 57918-2024 artfynd.xlsx
@@ -2411,7 +2411,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122083888</v>
+        <v>122083890</v>
       </c>
       <c r="B18" t="n">
         <v>57365</v>
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>418785</v>
+        <v>418789</v>
       </c>
       <c r="R18" t="n">
         <v>7053838</v>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2518,7 +2518,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122083890</v>
+        <v>122083888</v>
       </c>
       <c r="B19" t="n">
         <v>57365</v>
@@ -2558,7 +2558,7 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>418789</v>
+        <v>418785</v>
       </c>
       <c r="R19" t="n">
         <v>7053838</v>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2839,7 +2839,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122083874</v>
+        <v>122083876</v>
       </c>
       <c r="B22" t="n">
         <v>57365</v>
@@ -2879,10 +2879,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>418592</v>
+        <v>418613</v>
       </c>
       <c r="R22" t="n">
-        <v>7053670</v>
+        <v>7053668</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2946,7 +2946,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122083876</v>
+        <v>122083874</v>
       </c>
       <c r="B23" t="n">
         <v>57365</v>
@@ -2986,10 +2986,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>418613</v>
+        <v>418592</v>
       </c>
       <c r="R23" t="n">
-        <v>7053668</v>
+        <v>7053670</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 57918-2024 artfynd.xlsx
+++ b/artfynd/A 57918-2024 artfynd.xlsx
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122083902</v>
+        <v>122083893</v>
       </c>
       <c r="B4" t="n">
-        <v>57365</v>
+        <v>57369</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -953,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>418725</v>
+        <v>418775</v>
       </c>
       <c r="R4" t="n">
-        <v>7053592</v>
+        <v>7053757</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122083877</v>
+        <v>122083869</v>
       </c>
       <c r="B5" t="n">
-        <v>57365</v>
+        <v>57369</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1054,16 +1054,28 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gåstjärnvalen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>418615</v>
+        <v>418453</v>
       </c>
       <c r="R5" t="n">
-        <v>7053683</v>
+        <v>7053383</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,11 +1108,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-01-10</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,10 +1134,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122083875</v>
+        <v>122083902</v>
       </c>
       <c r="B6" t="n">
-        <v>57365</v>
+        <v>57369</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,10 +1174,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>418602</v>
+        <v>418725</v>
       </c>
       <c r="R6" t="n">
-        <v>7053668</v>
+        <v>7053592</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1234,10 +1241,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122083889</v>
+        <v>122083885</v>
       </c>
       <c r="B7" t="n">
-        <v>57365</v>
+        <v>57369</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1274,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>418787</v>
+        <v>418741</v>
       </c>
       <c r="R7" t="n">
-        <v>7053837</v>
+        <v>7053893</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,7 +1321,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1341,10 +1348,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122083868</v>
+        <v>122083871</v>
       </c>
       <c r="B8" t="n">
-        <v>57365</v>
+        <v>57369</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1381,10 +1388,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>418309</v>
+        <v>418491</v>
       </c>
       <c r="R8" t="n">
-        <v>7053279</v>
+        <v>7053452</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1448,10 +1455,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122083894</v>
+        <v>122083883</v>
       </c>
       <c r="B9" t="n">
-        <v>57365</v>
+        <v>57369</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1488,10 +1495,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>418782</v>
+        <v>418739</v>
       </c>
       <c r="R9" t="n">
-        <v>7053729</v>
+        <v>7053883</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1528,7 +1535,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1555,10 +1562,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122083896</v>
+        <v>122083868</v>
       </c>
       <c r="B10" t="n">
-        <v>57365</v>
+        <v>57369</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1595,10 +1602,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>418900</v>
+        <v>418309</v>
       </c>
       <c r="R10" t="n">
-        <v>7053621</v>
+        <v>7053279</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1635,7 +1642,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1662,10 +1669,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122083883</v>
+        <v>122083898</v>
       </c>
       <c r="B11" t="n">
-        <v>57365</v>
+        <v>57369</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1702,10 +1709,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>418739</v>
+        <v>418731</v>
       </c>
       <c r="R11" t="n">
-        <v>7053883</v>
+        <v>7053619</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1742,7 +1749,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1769,10 +1776,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122083892</v>
+        <v>122083886</v>
       </c>
       <c r="B12" t="n">
-        <v>57365</v>
+        <v>57369</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1809,10 +1816,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>418769</v>
+        <v>418755</v>
       </c>
       <c r="R12" t="n">
-        <v>7053764</v>
+        <v>7053901</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1849,7 +1856,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1876,10 +1883,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122083898</v>
+        <v>122083890</v>
       </c>
       <c r="B13" t="n">
-        <v>57365</v>
+        <v>57369</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1916,10 +1923,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>418731</v>
+        <v>418789</v>
       </c>
       <c r="R13" t="n">
-        <v>7053619</v>
+        <v>7053838</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1983,10 +1990,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122083904</v>
+        <v>122083887</v>
       </c>
       <c r="B14" t="n">
-        <v>78632</v>
+        <v>57369</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1999,21 +2006,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2023,10 +2030,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>418450</v>
+        <v>418757</v>
       </c>
       <c r="R14" t="n">
-        <v>7053262</v>
+        <v>7053896</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2063,7 +2070,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>riktigt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2090,10 +2097,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122083878</v>
+        <v>122083904</v>
       </c>
       <c r="B15" t="n">
-        <v>57365</v>
+        <v>78639</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2106,21 +2113,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2130,10 +2137,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>418620</v>
+        <v>418450</v>
       </c>
       <c r="R15" t="n">
-        <v>7053685</v>
+        <v>7053262</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2170,7 +2177,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>riktigt</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2197,10 +2204,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122083886</v>
+        <v>122083903</v>
       </c>
       <c r="B16" t="n">
-        <v>57365</v>
+        <v>57369</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2237,10 +2244,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>418755</v>
+        <v>418664</v>
       </c>
       <c r="R16" t="n">
-        <v>7053901</v>
+        <v>7053400</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2277,7 +2284,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2304,10 +2311,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122083903</v>
+        <v>122083878</v>
       </c>
       <c r="B17" t="n">
-        <v>57365</v>
+        <v>57369</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2344,10 +2351,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>418664</v>
+        <v>418620</v>
       </c>
       <c r="R17" t="n">
-        <v>7053400</v>
+        <v>7053685</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2411,10 +2418,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122083890</v>
+        <v>122083894</v>
       </c>
       <c r="B18" t="n">
-        <v>57365</v>
+        <v>57369</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2451,10 +2458,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>418789</v>
+        <v>418782</v>
       </c>
       <c r="R18" t="n">
-        <v>7053838</v>
+        <v>7053729</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2491,7 +2498,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2518,10 +2525,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122083888</v>
+        <v>122083874</v>
       </c>
       <c r="B19" t="n">
-        <v>57365</v>
+        <v>57369</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2558,10 +2565,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>418785</v>
+        <v>418592</v>
       </c>
       <c r="R19" t="n">
-        <v>7053838</v>
+        <v>7053670</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2625,10 +2632,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122083880</v>
+        <v>122083889</v>
       </c>
       <c r="B20" t="n">
-        <v>57365</v>
+        <v>57369</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2665,10 +2672,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>418705</v>
+        <v>418787</v>
       </c>
       <c r="R20" t="n">
-        <v>7053783</v>
+        <v>7053837</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2732,10 +2739,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122083871</v>
+        <v>122083876</v>
       </c>
       <c r="B21" t="n">
-        <v>57365</v>
+        <v>57369</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2772,10 +2779,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>418491</v>
+        <v>418613</v>
       </c>
       <c r="R21" t="n">
-        <v>7053452</v>
+        <v>7053668</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2812,7 +2819,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2839,10 +2846,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122083876</v>
+        <v>122083870</v>
       </c>
       <c r="B22" t="n">
-        <v>57365</v>
+        <v>57369</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2879,10 +2886,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>418613</v>
+        <v>418476</v>
       </c>
       <c r="R22" t="n">
-        <v>7053668</v>
+        <v>7053445</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2919,7 +2926,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2946,10 +2953,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122083874</v>
+        <v>122083875</v>
       </c>
       <c r="B23" t="n">
-        <v>57365</v>
+        <v>57369</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2986,10 +2993,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>418592</v>
+        <v>418602</v>
       </c>
       <c r="R23" t="n">
-        <v>7053670</v>
+        <v>7053668</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3026,7 +3033,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3053,10 +3060,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122083873</v>
+        <v>122083892</v>
       </c>
       <c r="B24" t="n">
-        <v>57365</v>
+        <v>57369</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3093,10 +3100,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>418544</v>
+        <v>418769</v>
       </c>
       <c r="R24" t="n">
-        <v>7053546</v>
+        <v>7053764</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3160,10 +3167,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122083869</v>
+        <v>122083896</v>
       </c>
       <c r="B25" t="n">
-        <v>57365</v>
+        <v>57369</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3194,28 +3201,16 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Gåstjärnvalen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>418453</v>
+        <v>418900</v>
       </c>
       <c r="R25" t="n">
-        <v>7053383</v>
+        <v>7053621</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3248,6 +3243,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3274,10 +3274,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122083897</v>
+        <v>122083873</v>
       </c>
       <c r="B26" t="n">
-        <v>57365</v>
+        <v>57369</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3314,10 +3314,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>418829</v>
+        <v>418544</v>
       </c>
       <c r="R26" t="n">
-        <v>7053675</v>
+        <v>7053546</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3381,10 +3381,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122083887</v>
+        <v>122083899</v>
       </c>
       <c r="B27" t="n">
-        <v>57365</v>
+        <v>57369</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3421,10 +3421,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>418757</v>
+        <v>418744</v>
       </c>
       <c r="R27" t="n">
-        <v>7053896</v>
+        <v>7053595</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3488,10 +3488,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122083882</v>
+        <v>122083888</v>
       </c>
       <c r="B28" t="n">
-        <v>57365</v>
+        <v>57369</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3528,10 +3528,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>418746</v>
+        <v>418785</v>
       </c>
       <c r="R28" t="n">
-        <v>7053865</v>
+        <v>7053838</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3568,7 +3568,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3595,10 +3595,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122083879</v>
+        <v>122083880</v>
       </c>
       <c r="B29" t="n">
-        <v>57365</v>
+        <v>57369</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>418631</v>
+        <v>418705</v>
       </c>
       <c r="R29" t="n">
-        <v>7053701</v>
+        <v>7053783</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3702,10 +3702,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122083885</v>
+        <v>122083901</v>
       </c>
       <c r="B30" t="n">
-        <v>57365</v>
+        <v>57369</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3742,10 +3742,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>418741</v>
+        <v>418735</v>
       </c>
       <c r="R30" t="n">
-        <v>7053893</v>
+        <v>7053591</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3809,10 +3809,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122083870</v>
+        <v>122083879</v>
       </c>
       <c r="B31" t="n">
-        <v>57365</v>
+        <v>57369</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3849,10 +3849,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>418476</v>
+        <v>418631</v>
       </c>
       <c r="R31" t="n">
-        <v>7053445</v>
+        <v>7053701</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3916,10 +3916,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122083895</v>
+        <v>122083891</v>
       </c>
       <c r="B32" t="n">
-        <v>57365</v>
+        <v>57369</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3956,10 +3956,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>418939</v>
+        <v>418789</v>
       </c>
       <c r="R32" t="n">
-        <v>7053794</v>
+        <v>7053772</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3996,7 +3996,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4023,10 +4023,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122083901</v>
+        <v>122083895</v>
       </c>
       <c r="B33" t="n">
-        <v>57365</v>
+        <v>57369</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4063,10 +4063,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>418735</v>
+        <v>418939</v>
       </c>
       <c r="R33" t="n">
-        <v>7053591</v>
+        <v>7053794</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4130,10 +4130,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122083893</v>
+        <v>122083881</v>
       </c>
       <c r="B34" t="n">
-        <v>57365</v>
+        <v>57369</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4170,10 +4170,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>418775</v>
+        <v>418710</v>
       </c>
       <c r="R34" t="n">
-        <v>7053757</v>
+        <v>7053790</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4237,10 +4237,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122083899</v>
+        <v>122083897</v>
       </c>
       <c r="B35" t="n">
-        <v>57365</v>
+        <v>57369</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4277,10 +4277,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>418744</v>
+        <v>418829</v>
       </c>
       <c r="R35" t="n">
-        <v>7053595</v>
+        <v>7053675</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4344,10 +4344,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122083881</v>
+        <v>122083877</v>
       </c>
       <c r="B36" t="n">
-        <v>57365</v>
+        <v>57369</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4384,10 +4384,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>418710</v>
+        <v>418615</v>
       </c>
       <c r="R36" t="n">
-        <v>7053790</v>
+        <v>7053683</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4424,7 +4424,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4451,10 +4451,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122083891</v>
+        <v>122083882</v>
       </c>
       <c r="B37" t="n">
-        <v>57365</v>
+        <v>57369</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4491,10 +4491,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>418789</v>
+        <v>418746</v>
       </c>
       <c r="R37" t="n">
-        <v>7053772</v>
+        <v>7053865</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 57918-2024 artfynd.xlsx
+++ b/artfynd/A 57918-2024 artfynd.xlsx
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122083893</v>
+        <v>122083884</v>
       </c>
       <c r="B4" t="n">
-        <v>57369</v>
+        <v>57372</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -953,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>418775</v>
+        <v>418739</v>
       </c>
       <c r="R4" t="n">
-        <v>7053757</v>
+        <v>7053883</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122083869</v>
+        <v>122083871</v>
       </c>
       <c r="B5" t="n">
-        <v>57369</v>
+        <v>57372</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1054,28 +1054,16 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gåstjärnvalen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>418453</v>
+        <v>418491</v>
       </c>
       <c r="R5" t="n">
-        <v>7053383</v>
+        <v>7053452</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,6 +1096,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122083902</v>
+        <v>122083898</v>
       </c>
       <c r="B6" t="n">
-        <v>57369</v>
+        <v>57372</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1174,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>418725</v>
+        <v>418731</v>
       </c>
       <c r="R6" t="n">
-        <v>7053592</v>
+        <v>7053619</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1241,10 +1234,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122083885</v>
+        <v>122083874</v>
       </c>
       <c r="B7" t="n">
-        <v>57369</v>
+        <v>57372</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1281,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>418741</v>
+        <v>418592</v>
       </c>
       <c r="R7" t="n">
-        <v>7053893</v>
+        <v>7053670</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1348,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122083871</v>
+        <v>122083881</v>
       </c>
       <c r="B8" t="n">
-        <v>57369</v>
+        <v>57372</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,10 +1381,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>418491</v>
+        <v>418710</v>
       </c>
       <c r="R8" t="n">
-        <v>7053452</v>
+        <v>7053790</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1428,7 +1421,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1455,10 +1448,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122083883</v>
+        <v>122083876</v>
       </c>
       <c r="B9" t="n">
-        <v>57369</v>
+        <v>57372</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,10 +1488,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>418739</v>
+        <v>418613</v>
       </c>
       <c r="R9" t="n">
-        <v>7053883</v>
+        <v>7053668</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1535,7 +1528,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1562,10 +1555,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122083868</v>
+        <v>122083878</v>
       </c>
       <c r="B10" t="n">
-        <v>57369</v>
+        <v>57372</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1602,10 +1595,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>418309</v>
+        <v>418620</v>
       </c>
       <c r="R10" t="n">
-        <v>7053279</v>
+        <v>7053685</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,10 +1662,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122083898</v>
+        <v>122083897</v>
       </c>
       <c r="B11" t="n">
-        <v>57369</v>
+        <v>57372</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1709,10 +1702,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>418731</v>
+        <v>418829</v>
       </c>
       <c r="R11" t="n">
-        <v>7053619</v>
+        <v>7053675</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1776,10 +1769,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122083886</v>
+        <v>122083896</v>
       </c>
       <c r="B12" t="n">
-        <v>57369</v>
+        <v>57372</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1816,10 +1809,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>418755</v>
+        <v>418900</v>
       </c>
       <c r="R12" t="n">
-        <v>7053901</v>
+        <v>7053621</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1883,10 +1876,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122083890</v>
+        <v>122083889</v>
       </c>
       <c r="B13" t="n">
-        <v>57369</v>
+        <v>57372</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1923,10 +1916,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>418789</v>
+        <v>418787</v>
       </c>
       <c r="R13" t="n">
-        <v>7053838</v>
+        <v>7053837</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1990,10 +1983,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122083887</v>
+        <v>122083885</v>
       </c>
       <c r="B14" t="n">
-        <v>57369</v>
+        <v>57372</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2030,10 +2023,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>418757</v>
+        <v>418741</v>
       </c>
       <c r="R14" t="n">
-        <v>7053896</v>
+        <v>7053893</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2070,7 +2063,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2100,7 +2093,7 @@
         <v>122083904</v>
       </c>
       <c r="B15" t="n">
-        <v>78639</v>
+        <v>78643</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2204,10 +2197,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122083903</v>
+        <v>122083899</v>
       </c>
       <c r="B16" t="n">
-        <v>57369</v>
+        <v>57372</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2244,10 +2237,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>418664</v>
+        <v>418744</v>
       </c>
       <c r="R16" t="n">
-        <v>7053400</v>
+        <v>7053595</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2311,10 +2304,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122083878</v>
+        <v>122083892</v>
       </c>
       <c r="B17" t="n">
-        <v>57369</v>
+        <v>57372</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2351,10 +2344,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>418620</v>
+        <v>418769</v>
       </c>
       <c r="R17" t="n">
-        <v>7053685</v>
+        <v>7053764</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2418,10 +2411,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122083894</v>
+        <v>122083886</v>
       </c>
       <c r="B18" t="n">
-        <v>57369</v>
+        <v>57372</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2458,10 +2451,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>418782</v>
+        <v>418755</v>
       </c>
       <c r="R18" t="n">
-        <v>7053729</v>
+        <v>7053901</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2525,10 +2518,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122083874</v>
+        <v>122083887</v>
       </c>
       <c r="B19" t="n">
-        <v>57369</v>
+        <v>57372</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2565,10 +2558,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>418592</v>
+        <v>418757</v>
       </c>
       <c r="R19" t="n">
-        <v>7053670</v>
+        <v>7053896</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2605,7 +2598,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2632,10 +2625,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122083889</v>
+        <v>122083879</v>
       </c>
       <c r="B20" t="n">
-        <v>57369</v>
+        <v>57372</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2672,10 +2665,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>418787</v>
+        <v>418631</v>
       </c>
       <c r="R20" t="n">
-        <v>7053837</v>
+        <v>7053701</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2739,10 +2732,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122083876</v>
+        <v>122083877</v>
       </c>
       <c r="B21" t="n">
-        <v>57369</v>
+        <v>57372</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2779,10 +2772,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>418613</v>
+        <v>418615</v>
       </c>
       <c r="R21" t="n">
-        <v>7053668</v>
+        <v>7053683</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2819,7 +2812,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2846,10 +2839,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122083870</v>
+        <v>122083882</v>
       </c>
       <c r="B22" t="n">
-        <v>57369</v>
+        <v>57372</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2886,10 +2879,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>418476</v>
+        <v>418746</v>
       </c>
       <c r="R22" t="n">
-        <v>7053445</v>
+        <v>7053865</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2953,10 +2946,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122083875</v>
+        <v>122083902</v>
       </c>
       <c r="B23" t="n">
-        <v>57369</v>
+        <v>57372</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2993,10 +2986,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>418602</v>
+        <v>418725</v>
       </c>
       <c r="R23" t="n">
-        <v>7053668</v>
+        <v>7053592</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3060,10 +3053,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122083892</v>
+        <v>122083895</v>
       </c>
       <c r="B24" t="n">
-        <v>57369</v>
+        <v>57372</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3100,10 +3093,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>418769</v>
+        <v>418939</v>
       </c>
       <c r="R24" t="n">
-        <v>7053764</v>
+        <v>7053794</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3167,10 +3160,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122083896</v>
+        <v>122083869</v>
       </c>
       <c r="B25" t="n">
-        <v>57369</v>
+        <v>57372</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3201,16 +3194,28 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Gåstjärnvalen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>418900</v>
+        <v>418453</v>
       </c>
       <c r="R25" t="n">
-        <v>7053621</v>
+        <v>7053383</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3243,11 +3248,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-01-10</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3274,10 +3274,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122083873</v>
+        <v>122083888</v>
       </c>
       <c r="B26" t="n">
-        <v>57369</v>
+        <v>57372</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3314,10 +3314,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>418544</v>
+        <v>418785</v>
       </c>
       <c r="R26" t="n">
-        <v>7053546</v>
+        <v>7053838</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3354,7 +3354,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3381,10 +3381,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122083899</v>
+        <v>122083894</v>
       </c>
       <c r="B27" t="n">
-        <v>57369</v>
+        <v>57372</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3421,10 +3421,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>418744</v>
+        <v>418782</v>
       </c>
       <c r="R27" t="n">
-        <v>7053595</v>
+        <v>7053729</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3461,7 +3461,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3488,10 +3488,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122083888</v>
+        <v>122083880</v>
       </c>
       <c r="B28" t="n">
-        <v>57369</v>
+        <v>57372</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3528,10 +3528,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>418785</v>
+        <v>418705</v>
       </c>
       <c r="R28" t="n">
-        <v>7053838</v>
+        <v>7053783</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3568,7 +3568,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3595,10 +3595,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122083880</v>
+        <v>122083875</v>
       </c>
       <c r="B29" t="n">
-        <v>57369</v>
+        <v>57372</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>418705</v>
+        <v>418602</v>
       </c>
       <c r="R29" t="n">
-        <v>7053783</v>
+        <v>7053668</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3702,10 +3702,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122083901</v>
+        <v>122083868</v>
       </c>
       <c r="B30" t="n">
-        <v>57369</v>
+        <v>57372</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3742,10 +3742,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>418735</v>
+        <v>418309</v>
       </c>
       <c r="R30" t="n">
-        <v>7053591</v>
+        <v>7053279</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3782,7 +3782,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3809,10 +3809,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122083879</v>
+        <v>122083891</v>
       </c>
       <c r="B31" t="n">
-        <v>57369</v>
+        <v>57372</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3849,10 +3849,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>418631</v>
+        <v>418789</v>
       </c>
       <c r="R31" t="n">
-        <v>7053701</v>
+        <v>7053772</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3916,10 +3916,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122083891</v>
+        <v>122083873</v>
       </c>
       <c r="B32" t="n">
-        <v>57369</v>
+        <v>57372</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3956,10 +3956,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>418789</v>
+        <v>418544</v>
       </c>
       <c r="R32" t="n">
-        <v>7053772</v>
+        <v>7053546</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3996,7 +3996,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4023,10 +4023,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122083895</v>
+        <v>122083893</v>
       </c>
       <c r="B33" t="n">
-        <v>57369</v>
+        <v>57372</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4063,10 +4063,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>418939</v>
+        <v>418775</v>
       </c>
       <c r="R33" t="n">
-        <v>7053794</v>
+        <v>7053757</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4130,10 +4130,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122083881</v>
+        <v>122083903</v>
       </c>
       <c r="B34" t="n">
-        <v>57369</v>
+        <v>57372</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4170,10 +4170,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>418710</v>
+        <v>418664</v>
       </c>
       <c r="R34" t="n">
-        <v>7053790</v>
+        <v>7053400</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4237,10 +4237,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122083897</v>
+        <v>122083890</v>
       </c>
       <c r="B35" t="n">
-        <v>57369</v>
+        <v>57372</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4277,10 +4277,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>418829</v>
+        <v>418789</v>
       </c>
       <c r="R35" t="n">
-        <v>7053675</v>
+        <v>7053838</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4344,10 +4344,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122083877</v>
+        <v>122083870</v>
       </c>
       <c r="B36" t="n">
-        <v>57369</v>
+        <v>57372</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4384,10 +4384,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>418615</v>
+        <v>418476</v>
       </c>
       <c r="R36" t="n">
-        <v>7053683</v>
+        <v>7053445</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4451,10 +4451,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122083882</v>
+        <v>122083901</v>
       </c>
       <c r="B37" t="n">
-        <v>57369</v>
+        <v>57372</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4491,10 +4491,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>418746</v>
+        <v>418735</v>
       </c>
       <c r="R37" t="n">
-        <v>7053865</v>
+        <v>7053591</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 57918-2024 artfynd.xlsx
+++ b/artfynd/A 57918-2024 artfynd.xlsx
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122083884</v>
+        <v>122083874</v>
       </c>
       <c r="B4" t="n">
-        <v>57372</v>
+        <v>57374</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -953,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>418739</v>
+        <v>418592</v>
       </c>
       <c r="R4" t="n">
-        <v>7053883</v>
+        <v>7053670</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +993,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122083871</v>
+        <v>122083877</v>
       </c>
       <c r="B5" t="n">
-        <v>57372</v>
+        <v>57374</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1060,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>418491</v>
+        <v>418615</v>
       </c>
       <c r="R5" t="n">
-        <v>7053452</v>
+        <v>7053683</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1127,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122083898</v>
+        <v>122083892</v>
       </c>
       <c r="B6" t="n">
-        <v>57372</v>
+        <v>57374</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>418731</v>
+        <v>418769</v>
       </c>
       <c r="R6" t="n">
-        <v>7053619</v>
+        <v>7053764</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1234,10 +1234,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122083874</v>
+        <v>122083893</v>
       </c>
       <c r="B7" t="n">
-        <v>57372</v>
+        <v>57374</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>418592</v>
+        <v>418775</v>
       </c>
       <c r="R7" t="n">
-        <v>7053670</v>
+        <v>7053757</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122083881</v>
+        <v>122083896</v>
       </c>
       <c r="B8" t="n">
-        <v>57372</v>
+        <v>57374</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>418710</v>
+        <v>418900</v>
       </c>
       <c r="R8" t="n">
-        <v>7053790</v>
+        <v>7053621</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1448,10 +1448,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122083876</v>
+        <v>122083878</v>
       </c>
       <c r="B9" t="n">
-        <v>57372</v>
+        <v>57374</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1488,10 +1488,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>418613</v>
+        <v>418620</v>
       </c>
       <c r="R9" t="n">
-        <v>7053668</v>
+        <v>7053685</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1555,10 +1555,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122083878</v>
+        <v>122083883</v>
       </c>
       <c r="B10" t="n">
-        <v>57372</v>
+        <v>57374</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1595,10 +1595,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>418620</v>
+        <v>418739</v>
       </c>
       <c r="R10" t="n">
-        <v>7053685</v>
+        <v>7053883</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1662,10 +1662,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122083897</v>
+        <v>122083898</v>
       </c>
       <c r="B11" t="n">
-        <v>57372</v>
+        <v>57374</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1702,10 +1702,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>418829</v>
+        <v>418731</v>
       </c>
       <c r="R11" t="n">
-        <v>7053675</v>
+        <v>7053619</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1769,10 +1769,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122083896</v>
+        <v>122083870</v>
       </c>
       <c r="B12" t="n">
-        <v>57372</v>
+        <v>57374</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1809,10 +1809,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>418900</v>
+        <v>418476</v>
       </c>
       <c r="R12" t="n">
-        <v>7053621</v>
+        <v>7053445</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1849,7 +1849,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1876,10 +1876,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122083889</v>
+        <v>122083901</v>
       </c>
       <c r="B13" t="n">
-        <v>57372</v>
+        <v>57374</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1916,10 +1916,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>418787</v>
+        <v>418735</v>
       </c>
       <c r="R13" t="n">
-        <v>7053837</v>
+        <v>7053591</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1956,7 +1956,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1983,10 +1983,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122083885</v>
+        <v>122083902</v>
       </c>
       <c r="B14" t="n">
-        <v>57372</v>
+        <v>57374</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2023,10 +2023,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>418741</v>
+        <v>418725</v>
       </c>
       <c r="R14" t="n">
-        <v>7053893</v>
+        <v>7053592</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2090,10 +2090,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122083904</v>
+        <v>122083888</v>
       </c>
       <c r="B15" t="n">
-        <v>78643</v>
+        <v>57374</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2106,21 +2106,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2130,10 +2130,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>418450</v>
+        <v>418785</v>
       </c>
       <c r="R15" t="n">
-        <v>7053262</v>
+        <v>7053838</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>riktigt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2197,10 +2197,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122083899</v>
+        <v>122083881</v>
       </c>
       <c r="B16" t="n">
-        <v>57372</v>
+        <v>57374</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2237,10 +2237,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>418744</v>
+        <v>418710</v>
       </c>
       <c r="R16" t="n">
-        <v>7053595</v>
+        <v>7053790</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2304,10 +2304,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122083892</v>
+        <v>122083879</v>
       </c>
       <c r="B17" t="n">
-        <v>57372</v>
+        <v>57374</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2344,10 +2344,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>418769</v>
+        <v>418631</v>
       </c>
       <c r="R17" t="n">
-        <v>7053764</v>
+        <v>7053701</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2411,10 +2411,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122083886</v>
+        <v>122083895</v>
       </c>
       <c r="B18" t="n">
-        <v>57372</v>
+        <v>57374</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2451,10 +2451,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>418755</v>
+        <v>418939</v>
       </c>
       <c r="R18" t="n">
-        <v>7053901</v>
+        <v>7053794</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2518,10 +2518,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122083887</v>
+        <v>122083889</v>
       </c>
       <c r="B19" t="n">
-        <v>57372</v>
+        <v>57374</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2558,10 +2558,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>418757</v>
+        <v>418787</v>
       </c>
       <c r="R19" t="n">
-        <v>7053896</v>
+        <v>7053837</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2625,10 +2625,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122083879</v>
+        <v>122083868</v>
       </c>
       <c r="B20" t="n">
-        <v>57372</v>
+        <v>57374</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2665,10 +2665,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>418631</v>
+        <v>418309</v>
       </c>
       <c r="R20" t="n">
-        <v>7053701</v>
+        <v>7053279</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2732,10 +2732,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122083877</v>
+        <v>122083885</v>
       </c>
       <c r="B21" t="n">
-        <v>57372</v>
+        <v>57374</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2772,10 +2772,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>418615</v>
+        <v>418741</v>
       </c>
       <c r="R21" t="n">
-        <v>7053683</v>
+        <v>7053893</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2812,7 +2812,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2839,10 +2839,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122083882</v>
+        <v>122083875</v>
       </c>
       <c r="B22" t="n">
-        <v>57372</v>
+        <v>57374</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2879,10 +2879,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>418746</v>
+        <v>418602</v>
       </c>
       <c r="R22" t="n">
-        <v>7053865</v>
+        <v>7053668</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2946,10 +2946,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122083902</v>
+        <v>122083904</v>
       </c>
       <c r="B23" t="n">
-        <v>57372</v>
+        <v>78645</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2962,21 +2962,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2986,10 +2986,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>418725</v>
+        <v>418450</v>
       </c>
       <c r="R23" t="n">
-        <v>7053592</v>
+        <v>7053262</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3026,7 +3026,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>riktigt</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3053,10 +3053,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122083895</v>
+        <v>122083897</v>
       </c>
       <c r="B24" t="n">
-        <v>57372</v>
+        <v>57374</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3093,10 +3093,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>418939</v>
+        <v>418829</v>
       </c>
       <c r="R24" t="n">
-        <v>7053794</v>
+        <v>7053675</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3163,7 +3163,7 @@
         <v>122083869</v>
       </c>
       <c r="B25" t="n">
-        <v>57372</v>
+        <v>57374</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3274,10 +3274,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122083888</v>
+        <v>122083873</v>
       </c>
       <c r="B26" t="n">
-        <v>57372</v>
+        <v>57374</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3314,10 +3314,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>418785</v>
+        <v>418544</v>
       </c>
       <c r="R26" t="n">
-        <v>7053838</v>
+        <v>7053546</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3354,7 +3354,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3381,10 +3381,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122083894</v>
+        <v>122083886</v>
       </c>
       <c r="B27" t="n">
-        <v>57372</v>
+        <v>57374</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3421,10 +3421,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>418782</v>
+        <v>418755</v>
       </c>
       <c r="R27" t="n">
-        <v>7053729</v>
+        <v>7053901</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3491,7 +3491,7 @@
         <v>122083880</v>
       </c>
       <c r="B28" t="n">
-        <v>57372</v>
+        <v>57374</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3595,10 +3595,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122083875</v>
+        <v>122083899</v>
       </c>
       <c r="B29" t="n">
-        <v>57372</v>
+        <v>57374</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>418602</v>
+        <v>418744</v>
       </c>
       <c r="R29" t="n">
-        <v>7053668</v>
+        <v>7053595</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3702,10 +3702,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122083868</v>
+        <v>122083887</v>
       </c>
       <c r="B30" t="n">
-        <v>57372</v>
+        <v>57374</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3742,10 +3742,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>418309</v>
+        <v>418757</v>
       </c>
       <c r="R30" t="n">
-        <v>7053279</v>
+        <v>7053896</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3809,10 +3809,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122083891</v>
+        <v>122083903</v>
       </c>
       <c r="B31" t="n">
-        <v>57372</v>
+        <v>57374</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3849,10 +3849,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>418789</v>
+        <v>418664</v>
       </c>
       <c r="R31" t="n">
-        <v>7053772</v>
+        <v>7053400</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3916,10 +3916,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122083873</v>
+        <v>122083891</v>
       </c>
       <c r="B32" t="n">
-        <v>57372</v>
+        <v>57374</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3956,10 +3956,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>418544</v>
+        <v>418789</v>
       </c>
       <c r="R32" t="n">
-        <v>7053546</v>
+        <v>7053772</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3996,7 +3996,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4023,10 +4023,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122083893</v>
+        <v>122083894</v>
       </c>
       <c r="B33" t="n">
-        <v>57372</v>
+        <v>57374</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4063,10 +4063,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>418775</v>
+        <v>418782</v>
       </c>
       <c r="R33" t="n">
-        <v>7053757</v>
+        <v>7053729</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4130,10 +4130,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122083903</v>
+        <v>122083871</v>
       </c>
       <c r="B34" t="n">
-        <v>57372</v>
+        <v>57374</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4170,10 +4170,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>418664</v>
+        <v>418491</v>
       </c>
       <c r="R34" t="n">
-        <v>7053400</v>
+        <v>7053452</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4237,10 +4237,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122083890</v>
+        <v>122083876</v>
       </c>
       <c r="B35" t="n">
-        <v>57372</v>
+        <v>57374</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4277,10 +4277,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>418789</v>
+        <v>418613</v>
       </c>
       <c r="R35" t="n">
-        <v>7053838</v>
+        <v>7053668</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4317,7 +4317,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4344,10 +4344,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122083870</v>
+        <v>122083882</v>
       </c>
       <c r="B36" t="n">
-        <v>57372</v>
+        <v>57374</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4384,10 +4384,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>418476</v>
+        <v>418746</v>
       </c>
       <c r="R36" t="n">
-        <v>7053445</v>
+        <v>7053865</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4451,10 +4451,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122083901</v>
+        <v>122083890</v>
       </c>
       <c r="B37" t="n">
-        <v>57372</v>
+        <v>57374</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4491,10 +4491,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>418735</v>
+        <v>418789</v>
       </c>
       <c r="R37" t="n">
-        <v>7053591</v>
+        <v>7053838</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 57918-2024 artfynd.xlsx
+++ b/artfynd/A 57918-2024 artfynd.xlsx
@@ -913,7 +913,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122083874</v>
+        <v>122083894</v>
       </c>
       <c r="B4" t="n">
         <v>57374</v>
@@ -953,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>418592</v>
+        <v>418782</v>
       </c>
       <c r="R4" t="n">
-        <v>7053670</v>
+        <v>7053729</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,7 +1020,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122083877</v>
+        <v>122083901</v>
       </c>
       <c r="B5" t="n">
         <v>57374</v>
@@ -1060,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>418615</v>
+        <v>418735</v>
       </c>
       <c r="R5" t="n">
-        <v>7053683</v>
+        <v>7053591</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,7 +1127,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122083892</v>
+        <v>122083889</v>
       </c>
       <c r="B6" t="n">
         <v>57374</v>
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>418769</v>
+        <v>418787</v>
       </c>
       <c r="R6" t="n">
-        <v>7053764</v>
+        <v>7053837</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1234,7 +1234,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122083893</v>
+        <v>122083885</v>
       </c>
       <c r="B7" t="n">
         <v>57374</v>
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>418775</v>
+        <v>418741</v>
       </c>
       <c r="R7" t="n">
-        <v>7053757</v>
+        <v>7053893</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1448,7 +1448,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122083878</v>
+        <v>122083902</v>
       </c>
       <c r="B9" t="n">
         <v>57374</v>
@@ -1488,10 +1488,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>418620</v>
+        <v>418725</v>
       </c>
       <c r="R9" t="n">
-        <v>7053685</v>
+        <v>7053592</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1555,7 +1555,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122083883</v>
+        <v>122083884</v>
       </c>
       <c r="B10" t="n">
         <v>57374</v>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1769,7 +1769,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122083870</v>
+        <v>122083891</v>
       </c>
       <c r="B12" t="n">
         <v>57374</v>
@@ -1809,10 +1809,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>418476</v>
+        <v>418789</v>
       </c>
       <c r="R12" t="n">
-        <v>7053445</v>
+        <v>7053772</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1849,7 +1849,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1876,7 +1876,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122083901</v>
+        <v>122083890</v>
       </c>
       <c r="B13" t="n">
         <v>57374</v>
@@ -1916,10 +1916,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>418735</v>
+        <v>418789</v>
       </c>
       <c r="R13" t="n">
-        <v>7053591</v>
+        <v>7053838</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1956,7 +1956,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1983,7 +1983,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122083902</v>
+        <v>122083897</v>
       </c>
       <c r="B14" t="n">
         <v>57374</v>
@@ -2023,10 +2023,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>418725</v>
+        <v>418829</v>
       </c>
       <c r="R14" t="n">
-        <v>7053592</v>
+        <v>7053675</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2090,7 +2090,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122083888</v>
+        <v>122083878</v>
       </c>
       <c r="B15" t="n">
         <v>57374</v>
@@ -2130,10 +2130,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>418785</v>
+        <v>418620</v>
       </c>
       <c r="R15" t="n">
-        <v>7053838</v>
+        <v>7053685</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2197,7 +2197,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122083881</v>
+        <v>122083893</v>
       </c>
       <c r="B16" t="n">
         <v>57374</v>
@@ -2237,10 +2237,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>418710</v>
+        <v>418775</v>
       </c>
       <c r="R16" t="n">
-        <v>7053790</v>
+        <v>7053757</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2304,7 +2304,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122083879</v>
+        <v>122083870</v>
       </c>
       <c r="B17" t="n">
         <v>57374</v>
@@ -2344,10 +2344,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>418631</v>
+        <v>418476</v>
       </c>
       <c r="R17" t="n">
-        <v>7053701</v>
+        <v>7053445</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2518,7 +2518,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122083889</v>
+        <v>122083874</v>
       </c>
       <c r="B19" t="n">
         <v>57374</v>
@@ -2558,10 +2558,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>418787</v>
+        <v>418592</v>
       </c>
       <c r="R19" t="n">
-        <v>7053837</v>
+        <v>7053670</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2625,7 +2625,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122083868</v>
+        <v>122083869</v>
       </c>
       <c r="B20" t="n">
         <v>57374</v>
@@ -2659,16 +2659,28 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Gåstjärnvalen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>418309</v>
+        <v>418453</v>
       </c>
       <c r="R20" t="n">
-        <v>7053279</v>
+        <v>7053383</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2701,11 +2713,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-01-10</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2732,7 +2739,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122083885</v>
+        <v>122083892</v>
       </c>
       <c r="B21" t="n">
         <v>57374</v>
@@ -2772,10 +2779,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>418741</v>
+        <v>418769</v>
       </c>
       <c r="R21" t="n">
-        <v>7053893</v>
+        <v>7053764</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2812,7 +2819,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2839,7 +2846,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122083875</v>
+        <v>122083882</v>
       </c>
       <c r="B22" t="n">
         <v>57374</v>
@@ -2879,10 +2886,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>418602</v>
+        <v>418746</v>
       </c>
       <c r="R22" t="n">
-        <v>7053668</v>
+        <v>7053865</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2946,10 +2953,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122083904</v>
+        <v>122083903</v>
       </c>
       <c r="B23" t="n">
-        <v>78645</v>
+        <v>57374</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2962,21 +2969,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2986,10 +2993,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>418450</v>
+        <v>418664</v>
       </c>
       <c r="R23" t="n">
-        <v>7053262</v>
+        <v>7053400</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3026,7 +3033,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>riktigt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3053,7 +3060,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122083897</v>
+        <v>122083887</v>
       </c>
       <c r="B24" t="n">
         <v>57374</v>
@@ -3093,10 +3100,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>418829</v>
+        <v>418757</v>
       </c>
       <c r="R24" t="n">
-        <v>7053675</v>
+        <v>7053896</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3160,7 +3167,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122083869</v>
+        <v>122083871</v>
       </c>
       <c r="B25" t="n">
         <v>57374</v>
@@ -3194,28 +3201,16 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Gåstjärnvalen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>418453</v>
+        <v>418491</v>
       </c>
       <c r="R25" t="n">
-        <v>7053383</v>
+        <v>7053452</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3248,6 +3243,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3274,7 +3274,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122083873</v>
+        <v>122083868</v>
       </c>
       <c r="B26" t="n">
         <v>57374</v>
@@ -3314,10 +3314,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>418544</v>
+        <v>418309</v>
       </c>
       <c r="R26" t="n">
-        <v>7053546</v>
+        <v>7053279</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3381,7 +3381,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122083886</v>
+        <v>122083873</v>
       </c>
       <c r="B27" t="n">
         <v>57374</v>
@@ -3421,10 +3421,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>418755</v>
+        <v>418544</v>
       </c>
       <c r="R27" t="n">
-        <v>7053901</v>
+        <v>7053546</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3461,7 +3461,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3488,7 +3488,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122083880</v>
+        <v>122083879</v>
       </c>
       <c r="B28" t="n">
         <v>57374</v>
@@ -3528,10 +3528,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>418705</v>
+        <v>418631</v>
       </c>
       <c r="R28" t="n">
-        <v>7053783</v>
+        <v>7053701</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3595,10 +3595,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122083899</v>
+        <v>122083904</v>
       </c>
       <c r="B29" t="n">
-        <v>57374</v>
+        <v>78645</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3611,21 +3611,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>418744</v>
+        <v>418450</v>
       </c>
       <c r="R29" t="n">
-        <v>7053595</v>
+        <v>7053262</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>riktigt</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3702,7 +3702,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122083887</v>
+        <v>122083877</v>
       </c>
       <c r="B30" t="n">
         <v>57374</v>
@@ -3742,10 +3742,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>418757</v>
+        <v>418615</v>
       </c>
       <c r="R30" t="n">
-        <v>7053896</v>
+        <v>7053683</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3809,7 +3809,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122083903</v>
+        <v>122083886</v>
       </c>
       <c r="B31" t="n">
         <v>57374</v>
@@ -3849,10 +3849,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>418664</v>
+        <v>418755</v>
       </c>
       <c r="R31" t="n">
-        <v>7053400</v>
+        <v>7053901</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3916,7 +3916,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122083891</v>
+        <v>122083888</v>
       </c>
       <c r="B32" t="n">
         <v>57374</v>
@@ -3956,10 +3956,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>418789</v>
+        <v>418785</v>
       </c>
       <c r="R32" t="n">
-        <v>7053772</v>
+        <v>7053838</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4023,7 +4023,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122083894</v>
+        <v>122083881</v>
       </c>
       <c r="B33" t="n">
         <v>57374</v>
@@ -4063,10 +4063,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>418782</v>
+        <v>418710</v>
       </c>
       <c r="R33" t="n">
-        <v>7053729</v>
+        <v>7053790</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4130,7 +4130,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122083871</v>
+        <v>122083880</v>
       </c>
       <c r="B34" t="n">
         <v>57374</v>
@@ -4170,10 +4170,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>418491</v>
+        <v>418705</v>
       </c>
       <c r="R34" t="n">
-        <v>7053452</v>
+        <v>7053783</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4237,7 +4237,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122083876</v>
+        <v>122083899</v>
       </c>
       <c r="B35" t="n">
         <v>57374</v>
@@ -4277,10 +4277,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>418613</v>
+        <v>418744</v>
       </c>
       <c r="R35" t="n">
-        <v>7053668</v>
+        <v>7053595</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4317,7 +4317,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4344,7 +4344,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122083882</v>
+        <v>122083876</v>
       </c>
       <c r="B36" t="n">
         <v>57374</v>
@@ -4384,10 +4384,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>418746</v>
+        <v>418613</v>
       </c>
       <c r="R36" t="n">
-        <v>7053865</v>
+        <v>7053668</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4424,7 +4424,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4451,7 +4451,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122083890</v>
+        <v>122083875</v>
       </c>
       <c r="B37" t="n">
         <v>57374</v>
@@ -4491,10 +4491,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>418789</v>
+        <v>418602</v>
       </c>
       <c r="R37" t="n">
-        <v>7053838</v>
+        <v>7053668</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>

--- a/artfynd/A 57918-2024 artfynd.xlsx
+++ b/artfynd/A 57918-2024 artfynd.xlsx
@@ -913,7 +913,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122083883</v>
+        <v>122083895</v>
       </c>
       <c r="B4" t="n">
         <v>57374</v>
@@ -953,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>418739</v>
+        <v>418939</v>
       </c>
       <c r="R4" t="n">
-        <v>7053883</v>
+        <v>7053794</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +993,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,7 +1020,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122083879</v>
+        <v>122083877</v>
       </c>
       <c r="B5" t="n">
         <v>57374</v>
@@ -1060,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>418631</v>
+        <v>418615</v>
       </c>
       <c r="R5" t="n">
-        <v>7053701</v>
+        <v>7053683</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1127,7 +1127,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122083890</v>
+        <v>122083902</v>
       </c>
       <c r="B6" t="n">
         <v>57374</v>
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>418789</v>
+        <v>418725</v>
       </c>
       <c r="R6" t="n">
-        <v>7053838</v>
+        <v>7053592</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1234,7 +1234,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122083871</v>
+        <v>122083884</v>
       </c>
       <c r="B7" t="n">
         <v>57374</v>
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>418491</v>
+        <v>418739</v>
       </c>
       <c r="R7" t="n">
-        <v>7053452</v>
+        <v>7053883</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,7 +1341,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122083874</v>
+        <v>122083869</v>
       </c>
       <c r="B8" t="n">
         <v>57374</v>
@@ -1375,16 +1375,28 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gåstjärnvalen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>418592</v>
+        <v>418453</v>
       </c>
       <c r="R8" t="n">
-        <v>7053670</v>
+        <v>7053383</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,11 +1429,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-01-10</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1448,7 +1455,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122083882</v>
+        <v>122083894</v>
       </c>
       <c r="B9" t="n">
         <v>57374</v>
@@ -1488,10 +1495,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>418746</v>
+        <v>418782</v>
       </c>
       <c r="R9" t="n">
-        <v>7053865</v>
+        <v>7053729</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1528,7 +1535,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1555,10 +1562,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122083891</v>
+        <v>122083904</v>
       </c>
       <c r="B10" t="n">
-        <v>57374</v>
+        <v>78645</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1571,21 +1578,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1595,10 +1602,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>418789</v>
+        <v>418450</v>
       </c>
       <c r="R10" t="n">
-        <v>7053772</v>
+        <v>7053262</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1635,7 +1642,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>riktigt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1662,7 +1669,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122083901</v>
+        <v>122083893</v>
       </c>
       <c r="B11" t="n">
         <v>57374</v>
@@ -1702,10 +1709,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>418735</v>
+        <v>418775</v>
       </c>
       <c r="R11" t="n">
-        <v>7053591</v>
+        <v>7053757</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1742,7 +1749,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1769,7 +1776,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122083880</v>
+        <v>122083876</v>
       </c>
       <c r="B12" t="n">
         <v>57374</v>
@@ -1809,10 +1816,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>418705</v>
+        <v>418613</v>
       </c>
       <c r="R12" t="n">
-        <v>7053783</v>
+        <v>7053668</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1849,7 +1856,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1983,7 +1990,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122083896</v>
+        <v>122083899</v>
       </c>
       <c r="B14" t="n">
         <v>57374</v>
@@ -2023,10 +2030,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>418900</v>
+        <v>418744</v>
       </c>
       <c r="R14" t="n">
-        <v>7053621</v>
+        <v>7053595</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2063,7 +2070,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2090,7 +2097,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122083881</v>
+        <v>122083879</v>
       </c>
       <c r="B15" t="n">
         <v>57374</v>
@@ -2130,10 +2137,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>418710</v>
+        <v>418631</v>
       </c>
       <c r="R15" t="n">
-        <v>7053790</v>
+        <v>7053701</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2170,7 +2177,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2197,7 +2204,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122083893</v>
+        <v>122083871</v>
       </c>
       <c r="B16" t="n">
         <v>57374</v>
@@ -2237,10 +2244,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>418775</v>
+        <v>418491</v>
       </c>
       <c r="R16" t="n">
-        <v>7053757</v>
+        <v>7053452</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2304,7 +2311,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122083898</v>
+        <v>122083874</v>
       </c>
       <c r="B17" t="n">
         <v>57374</v>
@@ -2344,10 +2351,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>418731</v>
+        <v>418592</v>
       </c>
       <c r="R17" t="n">
-        <v>7053619</v>
+        <v>7053670</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2384,7 +2391,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2411,7 +2418,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122083885</v>
+        <v>122083873</v>
       </c>
       <c r="B18" t="n">
         <v>57374</v>
@@ -2451,10 +2458,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>418741</v>
+        <v>418544</v>
       </c>
       <c r="R18" t="n">
-        <v>7053893</v>
+        <v>7053546</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2491,7 +2498,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2518,7 +2525,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122083886</v>
+        <v>122083892</v>
       </c>
       <c r="B19" t="n">
         <v>57374</v>
@@ -2558,10 +2565,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>418755</v>
+        <v>418769</v>
       </c>
       <c r="R19" t="n">
-        <v>7053901</v>
+        <v>7053764</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2598,7 +2605,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2625,7 +2632,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122083888</v>
+        <v>122083897</v>
       </c>
       <c r="B20" t="n">
         <v>57374</v>
@@ -2665,10 +2672,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>418785</v>
+        <v>418829</v>
       </c>
       <c r="R20" t="n">
-        <v>7053838</v>
+        <v>7053675</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2705,7 +2712,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2732,7 +2739,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122083875</v>
+        <v>122083891</v>
       </c>
       <c r="B21" t="n">
         <v>57374</v>
@@ -2772,10 +2779,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>418602</v>
+        <v>418789</v>
       </c>
       <c r="R21" t="n">
-        <v>7053668</v>
+        <v>7053772</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2812,7 +2819,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2839,7 +2846,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122083873</v>
+        <v>122083898</v>
       </c>
       <c r="B22" t="n">
         <v>57374</v>
@@ -2879,10 +2886,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>418544</v>
+        <v>418731</v>
       </c>
       <c r="R22" t="n">
-        <v>7053546</v>
+        <v>7053619</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2946,7 +2953,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122083899</v>
+        <v>122083889</v>
       </c>
       <c r="B23" t="n">
         <v>57374</v>
@@ -2986,10 +2993,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>418744</v>
+        <v>418787</v>
       </c>
       <c r="R23" t="n">
-        <v>7053595</v>
+        <v>7053837</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3053,7 +3060,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122083889</v>
+        <v>122083890</v>
       </c>
       <c r="B24" t="n">
         <v>57374</v>
@@ -3093,10 +3100,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>418787</v>
+        <v>418789</v>
       </c>
       <c r="R24" t="n">
-        <v>7053837</v>
+        <v>7053838</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3160,10 +3167,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122083904</v>
+        <v>122083887</v>
       </c>
       <c r="B25" t="n">
-        <v>78645</v>
+        <v>57374</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3176,21 +3183,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3200,10 +3207,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>418450</v>
+        <v>418757</v>
       </c>
       <c r="R25" t="n">
-        <v>7053262</v>
+        <v>7053896</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3240,7 +3247,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>riktigt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3267,7 +3274,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122083870</v>
+        <v>122083880</v>
       </c>
       <c r="B26" t="n">
         <v>57374</v>
@@ -3307,10 +3314,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>418476</v>
+        <v>418705</v>
       </c>
       <c r="R26" t="n">
-        <v>7053445</v>
+        <v>7053783</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3374,7 +3381,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122083877</v>
+        <v>122083896</v>
       </c>
       <c r="B27" t="n">
         <v>57374</v>
@@ -3414,10 +3421,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>418615</v>
+        <v>418900</v>
       </c>
       <c r="R27" t="n">
-        <v>7053683</v>
+        <v>7053621</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3454,7 +3461,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3481,7 +3488,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122083897</v>
+        <v>122083885</v>
       </c>
       <c r="B28" t="n">
         <v>57374</v>
@@ -3521,10 +3528,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>418829</v>
+        <v>418741</v>
       </c>
       <c r="R28" t="n">
-        <v>7053675</v>
+        <v>7053893</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3561,7 +3568,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3588,7 +3595,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122083892</v>
+        <v>122083901</v>
       </c>
       <c r="B29" t="n">
         <v>57374</v>
@@ -3628,10 +3635,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>418769</v>
+        <v>418735</v>
       </c>
       <c r="R29" t="n">
-        <v>7053764</v>
+        <v>7053591</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3668,7 +3675,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3695,7 +3702,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122083894</v>
+        <v>122083888</v>
       </c>
       <c r="B30" t="n">
         <v>57374</v>
@@ -3735,10 +3742,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>418782</v>
+        <v>418785</v>
       </c>
       <c r="R30" t="n">
-        <v>7053729</v>
+        <v>7053838</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3802,7 +3809,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122083869</v>
+        <v>122083882</v>
       </c>
       <c r="B31" t="n">
         <v>57374</v>
@@ -3836,28 +3843,16 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Gåstjärnvalen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>418453</v>
+        <v>418746</v>
       </c>
       <c r="R31" t="n">
-        <v>7053383</v>
+        <v>7053865</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3890,6 +3885,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3916,7 +3916,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122083902</v>
+        <v>122083878</v>
       </c>
       <c r="B32" t="n">
         <v>57374</v>
@@ -3956,10 +3956,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>418725</v>
+        <v>418620</v>
       </c>
       <c r="R32" t="n">
-        <v>7053592</v>
+        <v>7053685</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4023,7 +4023,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122083876</v>
+        <v>122083875</v>
       </c>
       <c r="B33" t="n">
         <v>57374</v>
@@ -4063,7 +4063,7 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>418613</v>
+        <v>418602</v>
       </c>
       <c r="R33" t="n">
         <v>7053668</v>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4130,7 +4130,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122083903</v>
+        <v>122083886</v>
       </c>
       <c r="B34" t="n">
         <v>57374</v>
@@ -4170,10 +4170,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>418664</v>
+        <v>418755</v>
       </c>
       <c r="R34" t="n">
-        <v>7053400</v>
+        <v>7053901</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4237,7 +4237,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122083895</v>
+        <v>122083870</v>
       </c>
       <c r="B35" t="n">
         <v>57374</v>
@@ -4277,10 +4277,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>418939</v>
+        <v>418476</v>
       </c>
       <c r="R35" t="n">
-        <v>7053794</v>
+        <v>7053445</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4344,7 +4344,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122083887</v>
+        <v>122083881</v>
       </c>
       <c r="B36" t="n">
         <v>57374</v>
@@ -4384,10 +4384,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>418757</v>
+        <v>418710</v>
       </c>
       <c r="R36" t="n">
-        <v>7053896</v>
+        <v>7053790</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4424,7 +4424,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4451,7 +4451,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122083878</v>
+        <v>122083903</v>
       </c>
       <c r="B37" t="n">
         <v>57374</v>
@@ -4491,10 +4491,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>418620</v>
+        <v>418664</v>
       </c>
       <c r="R37" t="n">
-        <v>7053685</v>
+        <v>7053400</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>

--- a/artfynd/A 57918-2024 artfynd.xlsx
+++ b/artfynd/A 57918-2024 artfynd.xlsx
@@ -913,7 +913,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122083895</v>
+        <v>122083874</v>
       </c>
       <c r="B4" t="n">
         <v>57374</v>
@@ -953,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>418939</v>
+        <v>418592</v>
       </c>
       <c r="R4" t="n">
-        <v>7053794</v>
+        <v>7053670</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +993,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,7 +1020,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122083877</v>
+        <v>122083869</v>
       </c>
       <c r="B5" t="n">
         <v>57374</v>
@@ -1054,16 +1054,28 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gåstjärnvalen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>418615</v>
+        <v>418453</v>
       </c>
       <c r="R5" t="n">
-        <v>7053683</v>
+        <v>7053383</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,11 +1108,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-01-10</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,7 +1134,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122083902</v>
+        <v>122083890</v>
       </c>
       <c r="B6" t="n">
         <v>57374</v>
@@ -1167,10 +1174,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>418725</v>
+        <v>418789</v>
       </c>
       <c r="R6" t="n">
-        <v>7053592</v>
+        <v>7053838</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1234,7 +1241,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122083884</v>
+        <v>122083880</v>
       </c>
       <c r="B7" t="n">
         <v>57374</v>
@@ -1274,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>418739</v>
+        <v>418705</v>
       </c>
       <c r="R7" t="n">
-        <v>7053883</v>
+        <v>7053783</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,7 +1348,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122083869</v>
+        <v>122083878</v>
       </c>
       <c r="B8" t="n">
         <v>57374</v>
@@ -1375,28 +1382,16 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gåstjärnvalen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>418453</v>
+        <v>418620</v>
       </c>
       <c r="R8" t="n">
-        <v>7053383</v>
+        <v>7053685</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1429,6 +1424,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1455,7 +1455,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122083894</v>
+        <v>122083871</v>
       </c>
       <c r="B9" t="n">
         <v>57374</v>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>418782</v>
+        <v>418491</v>
       </c>
       <c r="R9" t="n">
-        <v>7053729</v>
+        <v>7053452</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1535,7 +1535,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1562,10 +1562,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122083904</v>
+        <v>122083879</v>
       </c>
       <c r="B10" t="n">
-        <v>78645</v>
+        <v>57374</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1578,21 +1578,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>418450</v>
+        <v>418631</v>
       </c>
       <c r="R10" t="n">
-        <v>7053262</v>
+        <v>7053701</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1642,7 +1642,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>riktigt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1669,7 +1669,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122083893</v>
+        <v>122083877</v>
       </c>
       <c r="B11" t="n">
         <v>57374</v>
@@ -1709,10 +1709,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>418775</v>
+        <v>418615</v>
       </c>
       <c r="R11" t="n">
-        <v>7053757</v>
+        <v>7053683</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1776,7 +1776,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122083876</v>
+        <v>122083901</v>
       </c>
       <c r="B12" t="n">
         <v>57374</v>
@@ -1816,10 +1816,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>418613</v>
+        <v>418735</v>
       </c>
       <c r="R12" t="n">
-        <v>7053668</v>
+        <v>7053591</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1883,7 +1883,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122083868</v>
+        <v>122083889</v>
       </c>
       <c r="B13" t="n">
         <v>57374</v>
@@ -1923,10 +1923,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>418309</v>
+        <v>418787</v>
       </c>
       <c r="R13" t="n">
-        <v>7053279</v>
+        <v>7053837</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1990,7 +1990,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122083899</v>
+        <v>122083894</v>
       </c>
       <c r="B14" t="n">
         <v>57374</v>
@@ -2030,10 +2030,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>418744</v>
+        <v>418782</v>
       </c>
       <c r="R14" t="n">
-        <v>7053595</v>
+        <v>7053729</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2070,7 +2070,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2097,7 +2097,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122083879</v>
+        <v>122083896</v>
       </c>
       <c r="B15" t="n">
         <v>57374</v>
@@ -2137,10 +2137,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>418631</v>
+        <v>418900</v>
       </c>
       <c r="R15" t="n">
-        <v>7053701</v>
+        <v>7053621</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2177,7 +2177,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2204,7 +2204,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122083871</v>
+        <v>122083897</v>
       </c>
       <c r="B16" t="n">
         <v>57374</v>
@@ -2244,10 +2244,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>418491</v>
+        <v>418829</v>
       </c>
       <c r="R16" t="n">
-        <v>7053452</v>
+        <v>7053675</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2311,7 +2311,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122083874</v>
+        <v>122083888</v>
       </c>
       <c r="B17" t="n">
         <v>57374</v>
@@ -2351,10 +2351,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>418592</v>
+        <v>418785</v>
       </c>
       <c r="R17" t="n">
-        <v>7053670</v>
+        <v>7053838</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2418,7 +2418,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122083873</v>
+        <v>122083875</v>
       </c>
       <c r="B18" t="n">
         <v>57374</v>
@@ -2458,10 +2458,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>418544</v>
+        <v>418602</v>
       </c>
       <c r="R18" t="n">
-        <v>7053546</v>
+        <v>7053668</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2525,7 +2525,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122083892</v>
+        <v>122083882</v>
       </c>
       <c r="B19" t="n">
         <v>57374</v>
@@ -2565,10 +2565,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>418769</v>
+        <v>418746</v>
       </c>
       <c r="R19" t="n">
-        <v>7053764</v>
+        <v>7053865</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2632,7 +2632,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122083897</v>
+        <v>122083903</v>
       </c>
       <c r="B20" t="n">
         <v>57374</v>
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>418829</v>
+        <v>418664</v>
       </c>
       <c r="R20" t="n">
-        <v>7053675</v>
+        <v>7053400</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2739,7 +2739,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122083891</v>
+        <v>122083885</v>
       </c>
       <c r="B21" t="n">
         <v>57374</v>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>418789</v>
+        <v>418741</v>
       </c>
       <c r="R21" t="n">
-        <v>7053772</v>
+        <v>7053893</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2846,7 +2846,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122083898</v>
+        <v>122083893</v>
       </c>
       <c r="B22" t="n">
         <v>57374</v>
@@ -2886,10 +2886,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>418731</v>
+        <v>418775</v>
       </c>
       <c r="R22" t="n">
-        <v>7053619</v>
+        <v>7053757</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2953,7 +2953,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122083889</v>
+        <v>122083883</v>
       </c>
       <c r="B23" t="n">
         <v>57374</v>
@@ -2993,10 +2993,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>418787</v>
+        <v>418739</v>
       </c>
       <c r="R23" t="n">
-        <v>7053837</v>
+        <v>7053883</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3060,7 +3060,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122083890</v>
+        <v>122083881</v>
       </c>
       <c r="B24" t="n">
         <v>57374</v>
@@ -3100,10 +3100,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>418789</v>
+        <v>418710</v>
       </c>
       <c r="R24" t="n">
-        <v>7053838</v>
+        <v>7053790</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3167,7 +3167,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122083887</v>
+        <v>122083891</v>
       </c>
       <c r="B25" t="n">
         <v>57374</v>
@@ -3207,10 +3207,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>418757</v>
+        <v>418789</v>
       </c>
       <c r="R25" t="n">
-        <v>7053896</v>
+        <v>7053772</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3274,7 +3274,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122083880</v>
+        <v>122083892</v>
       </c>
       <c r="B26" t="n">
         <v>57374</v>
@@ -3314,10 +3314,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>418705</v>
+        <v>418769</v>
       </c>
       <c r="R26" t="n">
-        <v>7053783</v>
+        <v>7053764</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3381,7 +3381,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122083896</v>
+        <v>122083898</v>
       </c>
       <c r="B27" t="n">
         <v>57374</v>
@@ -3421,10 +3421,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>418900</v>
+        <v>418731</v>
       </c>
       <c r="R27" t="n">
-        <v>7053621</v>
+        <v>7053619</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3461,7 +3461,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3488,7 +3488,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122083885</v>
+        <v>122083899</v>
       </c>
       <c r="B28" t="n">
         <v>57374</v>
@@ -3528,10 +3528,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>418741</v>
+        <v>418744</v>
       </c>
       <c r="R28" t="n">
-        <v>7053893</v>
+        <v>7053595</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3568,7 +3568,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3595,7 +3595,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122083901</v>
+        <v>122083868</v>
       </c>
       <c r="B29" t="n">
         <v>57374</v>
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>418735</v>
+        <v>418309</v>
       </c>
       <c r="R29" t="n">
-        <v>7053591</v>
+        <v>7053279</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3702,7 +3702,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122083888</v>
+        <v>122083902</v>
       </c>
       <c r="B30" t="n">
         <v>57374</v>
@@ -3742,10 +3742,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>418785</v>
+        <v>418725</v>
       </c>
       <c r="R30" t="n">
-        <v>7053838</v>
+        <v>7053592</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3782,7 +3782,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3809,7 +3809,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122083882</v>
+        <v>122083895</v>
       </c>
       <c r="B31" t="n">
         <v>57374</v>
@@ -3849,10 +3849,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>418746</v>
+        <v>418939</v>
       </c>
       <c r="R31" t="n">
-        <v>7053865</v>
+        <v>7053794</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3916,7 +3916,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122083878</v>
+        <v>122083886</v>
       </c>
       <c r="B32" t="n">
         <v>57374</v>
@@ -3956,10 +3956,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>418620</v>
+        <v>418755</v>
       </c>
       <c r="R32" t="n">
-        <v>7053685</v>
+        <v>7053901</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3996,7 +3996,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4023,7 +4023,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122083875</v>
+        <v>122083873</v>
       </c>
       <c r="B33" t="n">
         <v>57374</v>
@@ -4063,10 +4063,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>418602</v>
+        <v>418544</v>
       </c>
       <c r="R33" t="n">
-        <v>7053668</v>
+        <v>7053546</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4130,7 +4130,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122083886</v>
+        <v>122083887</v>
       </c>
       <c r="B34" t="n">
         <v>57374</v>
@@ -4170,10 +4170,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>418755</v>
+        <v>418757</v>
       </c>
       <c r="R34" t="n">
-        <v>7053901</v>
+        <v>7053896</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4237,10 +4237,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122083870</v>
+        <v>122083904</v>
       </c>
       <c r="B35" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4253,21 +4253,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4277,10 +4277,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>418476</v>
+        <v>418450</v>
       </c>
       <c r="R35" t="n">
-        <v>7053445</v>
+        <v>7053262</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4317,7 +4317,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>riktigt</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4344,7 +4344,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122083881</v>
+        <v>122083870</v>
       </c>
       <c r="B36" t="n">
         <v>57374</v>
@@ -4384,10 +4384,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>418710</v>
+        <v>418476</v>
       </c>
       <c r="R36" t="n">
-        <v>7053790</v>
+        <v>7053445</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4424,7 +4424,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4451,7 +4451,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122083903</v>
+        <v>122083876</v>
       </c>
       <c r="B37" t="n">
         <v>57374</v>
@@ -4491,10 +4491,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>418664</v>
+        <v>418613</v>
       </c>
       <c r="R37" t="n">
-        <v>7053400</v>
+        <v>7053668</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 57918-2024 artfynd.xlsx
+++ b/artfynd/A 57918-2024 artfynd.xlsx
@@ -913,7 +913,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122083874</v>
+        <v>122083896</v>
       </c>
       <c r="B4" t="n">
         <v>57374</v>
@@ -953,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>418592</v>
+        <v>418900</v>
       </c>
       <c r="R4" t="n">
-        <v>7053670</v>
+        <v>7053621</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,7 +1020,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122083869</v>
+        <v>122083876</v>
       </c>
       <c r="B5" t="n">
         <v>57374</v>
@@ -1054,28 +1054,16 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gåstjärnvalen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>418453</v>
+        <v>418613</v>
       </c>
       <c r="R5" t="n">
-        <v>7053383</v>
+        <v>7053668</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,6 +1096,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,7 +1127,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122083890</v>
+        <v>122083887</v>
       </c>
       <c r="B6" t="n">
         <v>57374</v>
@@ -1174,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>418789</v>
+        <v>418757</v>
       </c>
       <c r="R6" t="n">
-        <v>7053838</v>
+        <v>7053896</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1241,7 +1234,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122083880</v>
+        <v>122083875</v>
       </c>
       <c r="B7" t="n">
         <v>57374</v>
@@ -1281,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>418705</v>
+        <v>418602</v>
       </c>
       <c r="R7" t="n">
-        <v>7053783</v>
+        <v>7053668</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1348,7 +1341,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122083878</v>
+        <v>122083894</v>
       </c>
       <c r="B8" t="n">
         <v>57374</v>
@@ -1388,10 +1381,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>418620</v>
+        <v>418782</v>
       </c>
       <c r="R8" t="n">
-        <v>7053685</v>
+        <v>7053729</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1428,7 +1421,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1455,7 +1448,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122083871</v>
+        <v>122083889</v>
       </c>
       <c r="B9" t="n">
         <v>57374</v>
@@ -1495,10 +1488,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>418491</v>
+        <v>418787</v>
       </c>
       <c r="R9" t="n">
-        <v>7053452</v>
+        <v>7053837</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1669,10 +1662,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122083877</v>
+        <v>122083904</v>
       </c>
       <c r="B11" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1685,21 +1678,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1709,10 +1702,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>418615</v>
+        <v>418450</v>
       </c>
       <c r="R11" t="n">
-        <v>7053683</v>
+        <v>7053262</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1749,7 +1742,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>riktigt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1776,7 +1769,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122083901</v>
+        <v>122083899</v>
       </c>
       <c r="B12" t="n">
         <v>57374</v>
@@ -1816,10 +1809,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>418735</v>
+        <v>418744</v>
       </c>
       <c r="R12" t="n">
-        <v>7053591</v>
+        <v>7053595</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1856,7 +1849,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1883,7 +1876,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122083889</v>
+        <v>122083892</v>
       </c>
       <c r="B13" t="n">
         <v>57374</v>
@@ -1923,10 +1916,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>418787</v>
+        <v>418769</v>
       </c>
       <c r="R13" t="n">
-        <v>7053837</v>
+        <v>7053764</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1990,7 +1983,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122083894</v>
+        <v>122083868</v>
       </c>
       <c r="B14" t="n">
         <v>57374</v>
@@ -2030,10 +2023,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>418782</v>
+        <v>418309</v>
       </c>
       <c r="R14" t="n">
-        <v>7053729</v>
+        <v>7053279</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2070,7 +2063,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2097,7 +2090,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122083896</v>
+        <v>122083898</v>
       </c>
       <c r="B15" t="n">
         <v>57374</v>
@@ -2137,10 +2130,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>418900</v>
+        <v>418731</v>
       </c>
       <c r="R15" t="n">
-        <v>7053621</v>
+        <v>7053619</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2177,7 +2170,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2204,7 +2197,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122083897</v>
+        <v>122083890</v>
       </c>
       <c r="B16" t="n">
         <v>57374</v>
@@ -2244,10 +2237,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>418829</v>
+        <v>418789</v>
       </c>
       <c r="R16" t="n">
-        <v>7053675</v>
+        <v>7053838</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2311,7 +2304,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122083888</v>
+        <v>122083882</v>
       </c>
       <c r="B17" t="n">
         <v>57374</v>
@@ -2351,10 +2344,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>418785</v>
+        <v>418746</v>
       </c>
       <c r="R17" t="n">
-        <v>7053838</v>
+        <v>7053865</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2391,7 +2384,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2418,7 +2411,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122083875</v>
+        <v>122083878</v>
       </c>
       <c r="B18" t="n">
         <v>57374</v>
@@ -2458,10 +2451,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>418602</v>
+        <v>418620</v>
       </c>
       <c r="R18" t="n">
-        <v>7053668</v>
+        <v>7053685</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2525,7 +2518,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122083882</v>
+        <v>122083886</v>
       </c>
       <c r="B19" t="n">
         <v>57374</v>
@@ -2565,10 +2558,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>418746</v>
+        <v>418755</v>
       </c>
       <c r="R19" t="n">
-        <v>7053865</v>
+        <v>7053901</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2605,7 +2598,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2632,7 +2625,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122083903</v>
+        <v>122083888</v>
       </c>
       <c r="B20" t="n">
         <v>57374</v>
@@ -2672,10 +2665,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>418664</v>
+        <v>418785</v>
       </c>
       <c r="R20" t="n">
-        <v>7053400</v>
+        <v>7053838</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2712,7 +2705,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2739,7 +2732,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122083885</v>
+        <v>122083903</v>
       </c>
       <c r="B21" t="n">
         <v>57374</v>
@@ -2779,10 +2772,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>418741</v>
+        <v>418664</v>
       </c>
       <c r="R21" t="n">
-        <v>7053893</v>
+        <v>7053400</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2819,7 +2812,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2846,7 +2839,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122083893</v>
+        <v>122083874</v>
       </c>
       <c r="B22" t="n">
         <v>57374</v>
@@ -2886,10 +2879,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>418775</v>
+        <v>418592</v>
       </c>
       <c r="R22" t="n">
-        <v>7053757</v>
+        <v>7053670</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2926,7 +2919,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2953,7 +2946,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122083883</v>
+        <v>122083871</v>
       </c>
       <c r="B23" t="n">
         <v>57374</v>
@@ -2993,10 +2986,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>418739</v>
+        <v>418491</v>
       </c>
       <c r="R23" t="n">
-        <v>7053883</v>
+        <v>7053452</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3033,7 +3026,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3060,7 +3053,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122083881</v>
+        <v>122083897</v>
       </c>
       <c r="B24" t="n">
         <v>57374</v>
@@ -3100,10 +3093,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>418710</v>
+        <v>418829</v>
       </c>
       <c r="R24" t="n">
-        <v>7053790</v>
+        <v>7053675</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3140,7 +3133,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3167,7 +3160,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122083891</v>
+        <v>122083881</v>
       </c>
       <c r="B25" t="n">
         <v>57374</v>
@@ -3207,10 +3200,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>418789</v>
+        <v>418710</v>
       </c>
       <c r="R25" t="n">
-        <v>7053772</v>
+        <v>7053790</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3247,7 +3240,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3274,7 +3267,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122083892</v>
+        <v>122083891</v>
       </c>
       <c r="B26" t="n">
         <v>57374</v>
@@ -3314,10 +3307,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>418769</v>
+        <v>418789</v>
       </c>
       <c r="R26" t="n">
-        <v>7053764</v>
+        <v>7053772</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3354,7 +3347,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3381,7 +3374,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122083898</v>
+        <v>122083869</v>
       </c>
       <c r="B27" t="n">
         <v>57374</v>
@@ -3415,16 +3408,28 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Gåstjärnvalen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>418731</v>
+        <v>418453</v>
       </c>
       <c r="R27" t="n">
-        <v>7053619</v>
+        <v>7053383</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3457,11 +3462,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-01-10</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3488,7 +3488,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122083899</v>
+        <v>122083895</v>
       </c>
       <c r="B28" t="n">
         <v>57374</v>
@@ -3528,10 +3528,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>418744</v>
+        <v>418939</v>
       </c>
       <c r="R28" t="n">
-        <v>7053595</v>
+        <v>7053794</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3595,7 +3595,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122083868</v>
+        <v>122083902</v>
       </c>
       <c r="B29" t="n">
         <v>57374</v>
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>418309</v>
+        <v>418725</v>
       </c>
       <c r="R29" t="n">
-        <v>7053279</v>
+        <v>7053592</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3702,7 +3702,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122083902</v>
+        <v>122083880</v>
       </c>
       <c r="B30" t="n">
         <v>57374</v>
@@ -3742,10 +3742,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>418725</v>
+        <v>418705</v>
       </c>
       <c r="R30" t="n">
-        <v>7053592</v>
+        <v>7053783</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3809,7 +3809,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122083895</v>
+        <v>122083885</v>
       </c>
       <c r="B31" t="n">
         <v>57374</v>
@@ -3849,10 +3849,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>418939</v>
+        <v>418741</v>
       </c>
       <c r="R31" t="n">
-        <v>7053794</v>
+        <v>7053893</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3916,7 +3916,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122083886</v>
+        <v>122083877</v>
       </c>
       <c r="B32" t="n">
         <v>57374</v>
@@ -3956,10 +3956,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>418755</v>
+        <v>418615</v>
       </c>
       <c r="R32" t="n">
-        <v>7053901</v>
+        <v>7053683</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3996,7 +3996,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4023,7 +4023,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122083873</v>
+        <v>122083870</v>
       </c>
       <c r="B33" t="n">
         <v>57374</v>
@@ -4063,10 +4063,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>418544</v>
+        <v>418476</v>
       </c>
       <c r="R33" t="n">
-        <v>7053546</v>
+        <v>7053445</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4130,7 +4130,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122083887</v>
+        <v>122083883</v>
       </c>
       <c r="B34" t="n">
         <v>57374</v>
@@ -4170,10 +4170,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>418757</v>
+        <v>418739</v>
       </c>
       <c r="R34" t="n">
-        <v>7053896</v>
+        <v>7053883</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4237,10 +4237,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122083904</v>
+        <v>122083873</v>
       </c>
       <c r="B35" t="n">
-        <v>78646</v>
+        <v>57374</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4253,21 +4253,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4277,10 +4277,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>418450</v>
+        <v>418544</v>
       </c>
       <c r="R35" t="n">
-        <v>7053262</v>
+        <v>7053546</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4317,7 +4317,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>riktigt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4344,7 +4344,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122083870</v>
+        <v>122083901</v>
       </c>
       <c r="B36" t="n">
         <v>57374</v>
@@ -4384,10 +4384,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>418476</v>
+        <v>418735</v>
       </c>
       <c r="R36" t="n">
-        <v>7053445</v>
+        <v>7053591</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4424,7 +4424,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4451,7 +4451,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122083876</v>
+        <v>122083893</v>
       </c>
       <c r="B37" t="n">
         <v>57374</v>
@@ -4491,10 +4491,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>418613</v>
+        <v>418775</v>
       </c>
       <c r="R37" t="n">
-        <v>7053668</v>
+        <v>7053757</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 57918-2024 artfynd.xlsx
+++ b/artfynd/A 57918-2024 artfynd.xlsx
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122083896</v>
+        <v>122083874</v>
       </c>
       <c r="B4" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -953,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>418900</v>
+        <v>418592</v>
       </c>
       <c r="R4" t="n">
-        <v>7053621</v>
+        <v>7053670</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122083876</v>
+        <v>122083893</v>
       </c>
       <c r="B5" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1060,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>418613</v>
+        <v>418775</v>
       </c>
       <c r="R5" t="n">
-        <v>7053668</v>
+        <v>7053757</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122083887</v>
+        <v>122083903</v>
       </c>
       <c r="B6" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>418757</v>
+        <v>418664</v>
       </c>
       <c r="R6" t="n">
-        <v>7053896</v>
+        <v>7053400</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1234,10 +1234,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122083875</v>
+        <v>122083881</v>
       </c>
       <c r="B7" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>418602</v>
+        <v>418710</v>
       </c>
       <c r="R7" t="n">
-        <v>7053668</v>
+        <v>7053790</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122083894</v>
+        <v>122083873</v>
       </c>
       <c r="B8" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>418782</v>
+        <v>418544</v>
       </c>
       <c r="R8" t="n">
-        <v>7053729</v>
+        <v>7053546</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1448,10 +1448,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122083889</v>
+        <v>122083880</v>
       </c>
       <c r="B9" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1488,10 +1488,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>418787</v>
+        <v>418705</v>
       </c>
       <c r="R9" t="n">
-        <v>7053837</v>
+        <v>7053783</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1555,10 +1555,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122083879</v>
+        <v>122083875</v>
       </c>
       <c r="B10" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1595,10 +1595,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>418631</v>
+        <v>418602</v>
       </c>
       <c r="R10" t="n">
-        <v>7053701</v>
+        <v>7053668</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1662,10 +1662,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122083904</v>
+        <v>122083895</v>
       </c>
       <c r="B11" t="n">
-        <v>78646</v>
+        <v>57379</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1678,21 +1678,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1702,10 +1702,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>418450</v>
+        <v>418939</v>
       </c>
       <c r="R11" t="n">
-        <v>7053262</v>
+        <v>7053794</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>riktigt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1769,10 +1769,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122083899</v>
+        <v>122083901</v>
       </c>
       <c r="B12" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1809,10 +1809,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>418744</v>
+        <v>418735</v>
       </c>
       <c r="R12" t="n">
-        <v>7053595</v>
+        <v>7053591</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1849,7 +1849,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1876,10 +1876,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122083892</v>
+        <v>122083887</v>
       </c>
       <c r="B13" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1916,10 +1916,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>418769</v>
+        <v>418757</v>
       </c>
       <c r="R13" t="n">
-        <v>7053764</v>
+        <v>7053896</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1983,10 +1983,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122083868</v>
+        <v>122083904</v>
       </c>
       <c r="B14" t="n">
-        <v>57374</v>
+        <v>78651</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1999,21 +1999,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2023,10 +2023,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>418309</v>
+        <v>418450</v>
       </c>
       <c r="R14" t="n">
-        <v>7053279</v>
+        <v>7053262</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>riktigt</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2090,10 +2090,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122083898</v>
+        <v>122083888</v>
       </c>
       <c r="B15" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2130,10 +2130,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>418731</v>
+        <v>418785</v>
       </c>
       <c r="R15" t="n">
-        <v>7053619</v>
+        <v>7053838</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2200,7 +2200,7 @@
         <v>122083890</v>
       </c>
       <c r="B16" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2304,10 +2304,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122083882</v>
+        <v>122083902</v>
       </c>
       <c r="B17" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2344,10 +2344,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>418746</v>
+        <v>418725</v>
       </c>
       <c r="R17" t="n">
-        <v>7053865</v>
+        <v>7053592</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2411,10 +2411,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122083878</v>
+        <v>122083894</v>
       </c>
       <c r="B18" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2451,10 +2451,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>418620</v>
+        <v>418782</v>
       </c>
       <c r="R18" t="n">
-        <v>7053685</v>
+        <v>7053729</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2518,10 +2518,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122083886</v>
+        <v>122083877</v>
       </c>
       <c r="B19" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2558,10 +2558,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>418755</v>
+        <v>418615</v>
       </c>
       <c r="R19" t="n">
-        <v>7053901</v>
+        <v>7053683</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2625,10 +2625,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122083888</v>
+        <v>122083879</v>
       </c>
       <c r="B20" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2665,10 +2665,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>418785</v>
+        <v>418631</v>
       </c>
       <c r="R20" t="n">
-        <v>7053838</v>
+        <v>7053701</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2705,7 +2705,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2732,10 +2732,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122083903</v>
+        <v>122083898</v>
       </c>
       <c r="B21" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2772,10 +2772,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>418664</v>
+        <v>418731</v>
       </c>
       <c r="R21" t="n">
-        <v>7053400</v>
+        <v>7053619</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2839,10 +2839,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122083874</v>
+        <v>122083870</v>
       </c>
       <c r="B22" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2879,10 +2879,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>418592</v>
+        <v>418476</v>
       </c>
       <c r="R22" t="n">
-        <v>7053670</v>
+        <v>7053445</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2919,7 +2919,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2946,10 +2946,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122083871</v>
+        <v>122083885</v>
       </c>
       <c r="B23" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2986,10 +2986,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>418491</v>
+        <v>418741</v>
       </c>
       <c r="R23" t="n">
-        <v>7053452</v>
+        <v>7053893</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3026,7 +3026,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3053,10 +3053,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122083897</v>
+        <v>122083892</v>
       </c>
       <c r="B24" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3093,10 +3093,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>418829</v>
+        <v>418769</v>
       </c>
       <c r="R24" t="n">
-        <v>7053675</v>
+        <v>7053764</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3160,10 +3160,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122083881</v>
+        <v>122083871</v>
       </c>
       <c r="B25" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3200,10 +3200,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>418710</v>
+        <v>418491</v>
       </c>
       <c r="R25" t="n">
-        <v>7053790</v>
+        <v>7053452</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3267,10 +3267,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122083891</v>
+        <v>122083878</v>
       </c>
       <c r="B26" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3307,10 +3307,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>418789</v>
+        <v>418620</v>
       </c>
       <c r="R26" t="n">
-        <v>7053772</v>
+        <v>7053685</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3347,7 +3347,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3374,10 +3374,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122083869</v>
+        <v>122083886</v>
       </c>
       <c r="B27" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3408,28 +3408,16 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Gåstjärnvalen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>418453</v>
+        <v>418755</v>
       </c>
       <c r="R27" t="n">
-        <v>7053383</v>
+        <v>7053901</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3462,6 +3450,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3488,10 +3481,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122083895</v>
+        <v>122083883</v>
       </c>
       <c r="B28" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3528,10 +3521,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>418939</v>
+        <v>418739</v>
       </c>
       <c r="R28" t="n">
-        <v>7053794</v>
+        <v>7053883</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3568,7 +3561,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3595,10 +3588,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122083902</v>
+        <v>122083897</v>
       </c>
       <c r="B29" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3635,10 +3628,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>418725</v>
+        <v>418829</v>
       </c>
       <c r="R29" t="n">
-        <v>7053592</v>
+        <v>7053675</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3702,10 +3695,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122083880</v>
+        <v>122083889</v>
       </c>
       <c r="B30" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3742,10 +3735,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>418705</v>
+        <v>418787</v>
       </c>
       <c r="R30" t="n">
-        <v>7053783</v>
+        <v>7053837</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3809,10 +3802,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122083885</v>
+        <v>122083876</v>
       </c>
       <c r="B31" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3849,10 +3842,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>418741</v>
+        <v>418613</v>
       </c>
       <c r="R31" t="n">
-        <v>7053893</v>
+        <v>7053668</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3916,10 +3909,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122083877</v>
+        <v>122083891</v>
       </c>
       <c r="B32" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3956,10 +3949,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>418615</v>
+        <v>418789</v>
       </c>
       <c r="R32" t="n">
-        <v>7053683</v>
+        <v>7053772</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3996,7 +3989,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4023,10 +4016,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122083870</v>
+        <v>122083896</v>
       </c>
       <c r="B33" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4063,10 +4056,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>418476</v>
+        <v>418900</v>
       </c>
       <c r="R33" t="n">
-        <v>7053445</v>
+        <v>7053621</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4103,7 +4096,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4130,10 +4123,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122083883</v>
+        <v>122083868</v>
       </c>
       <c r="B34" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4170,10 +4163,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>418739</v>
+        <v>418309</v>
       </c>
       <c r="R34" t="n">
-        <v>7053883</v>
+        <v>7053279</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4210,7 +4203,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4237,10 +4230,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122083873</v>
+        <v>122083869</v>
       </c>
       <c r="B35" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4271,16 +4264,28 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Gåstjärnvalen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>418544</v>
+        <v>418453</v>
       </c>
       <c r="R35" t="n">
-        <v>7053546</v>
+        <v>7053383</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4313,11 +4318,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-01-10</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4344,10 +4344,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122083901</v>
+        <v>122083882</v>
       </c>
       <c r="B36" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4384,10 +4384,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>418735</v>
+        <v>418746</v>
       </c>
       <c r="R36" t="n">
-        <v>7053591</v>
+        <v>7053865</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4424,7 +4424,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4451,10 +4451,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122083893</v>
+        <v>122083899</v>
       </c>
       <c r="B37" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4491,10 +4491,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>418775</v>
+        <v>418744</v>
       </c>
       <c r="R37" t="n">
-        <v>7053757</v>
+        <v>7053595</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>

--- a/artfynd/A 57918-2024 artfynd.xlsx
+++ b/artfynd/A 57918-2024 artfynd.xlsx
@@ -913,7 +913,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122083874</v>
+        <v>122083896</v>
       </c>
       <c r="B4" t="n">
         <v>57379</v>
@@ -953,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>418592</v>
+        <v>418900</v>
       </c>
       <c r="R4" t="n">
-        <v>7053670</v>
+        <v>7053621</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,7 +1020,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122083893</v>
+        <v>122083887</v>
       </c>
       <c r="B5" t="n">
         <v>57379</v>
@@ -1060,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>418775</v>
+        <v>418757</v>
       </c>
       <c r="R5" t="n">
-        <v>7053757</v>
+        <v>7053896</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1127,7 +1127,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122083903</v>
+        <v>122083888</v>
       </c>
       <c r="B6" t="n">
         <v>57379</v>
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>418664</v>
+        <v>418785</v>
       </c>
       <c r="R6" t="n">
-        <v>7053400</v>
+        <v>7053838</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1234,7 +1234,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122083881</v>
+        <v>122083885</v>
       </c>
       <c r="B7" t="n">
         <v>57379</v>
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>418710</v>
+        <v>418741</v>
       </c>
       <c r="R7" t="n">
-        <v>7053790</v>
+        <v>7053893</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1341,7 +1341,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122083873</v>
+        <v>122083877</v>
       </c>
       <c r="B8" t="n">
         <v>57379</v>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>418544</v>
+        <v>418615</v>
       </c>
       <c r="R8" t="n">
-        <v>7053546</v>
+        <v>7053683</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1448,7 +1448,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122083880</v>
+        <v>122083876</v>
       </c>
       <c r="B9" t="n">
         <v>57379</v>
@@ -1488,10 +1488,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>418705</v>
+        <v>418613</v>
       </c>
       <c r="R9" t="n">
-        <v>7053783</v>
+        <v>7053668</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1555,7 +1555,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122083875</v>
+        <v>122083878</v>
       </c>
       <c r="B10" t="n">
         <v>57379</v>
@@ -1595,10 +1595,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>418602</v>
+        <v>418620</v>
       </c>
       <c r="R10" t="n">
-        <v>7053668</v>
+        <v>7053685</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1662,7 +1662,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122083895</v>
+        <v>122083884</v>
       </c>
       <c r="B11" t="n">
         <v>57379</v>
@@ -1702,10 +1702,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>418939</v>
+        <v>418739</v>
       </c>
       <c r="R11" t="n">
-        <v>7053794</v>
+        <v>7053883</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1769,7 +1769,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122083901</v>
+        <v>122083875</v>
       </c>
       <c r="B12" t="n">
         <v>57379</v>
@@ -1809,10 +1809,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>418735</v>
+        <v>418602</v>
       </c>
       <c r="R12" t="n">
-        <v>7053591</v>
+        <v>7053668</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1849,7 +1849,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1876,7 +1876,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122083887</v>
+        <v>122083901</v>
       </c>
       <c r="B13" t="n">
         <v>57379</v>
@@ -1916,10 +1916,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>418757</v>
+        <v>418735</v>
       </c>
       <c r="R13" t="n">
-        <v>7053896</v>
+        <v>7053591</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1956,7 +1956,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1983,10 +1983,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122083904</v>
+        <v>122083903</v>
       </c>
       <c r="B14" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1999,21 +1999,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2023,10 +2023,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>418450</v>
+        <v>418664</v>
       </c>
       <c r="R14" t="n">
-        <v>7053262</v>
+        <v>7053400</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>riktigt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2090,7 +2090,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122083888</v>
+        <v>122083879</v>
       </c>
       <c r="B15" t="n">
         <v>57379</v>
@@ -2130,10 +2130,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>418785</v>
+        <v>418631</v>
       </c>
       <c r="R15" t="n">
-        <v>7053838</v>
+        <v>7053701</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2197,7 +2197,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122083890</v>
+        <v>122083880</v>
       </c>
       <c r="B16" t="n">
         <v>57379</v>
@@ -2237,10 +2237,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>418789</v>
+        <v>418705</v>
       </c>
       <c r="R16" t="n">
-        <v>7053838</v>
+        <v>7053783</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2304,7 +2304,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122083902</v>
+        <v>122083873</v>
       </c>
       <c r="B17" t="n">
         <v>57379</v>
@@ -2344,10 +2344,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>418725</v>
+        <v>418544</v>
       </c>
       <c r="R17" t="n">
-        <v>7053592</v>
+        <v>7053546</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2411,7 +2411,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122083894</v>
+        <v>122083899</v>
       </c>
       <c r="B18" t="n">
         <v>57379</v>
@@ -2451,10 +2451,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>418782</v>
+        <v>418744</v>
       </c>
       <c r="R18" t="n">
-        <v>7053729</v>
+        <v>7053595</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2518,7 +2518,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122083877</v>
+        <v>122083871</v>
       </c>
       <c r="B19" t="n">
         <v>57379</v>
@@ -2558,10 +2558,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>418615</v>
+        <v>418491</v>
       </c>
       <c r="R19" t="n">
-        <v>7053683</v>
+        <v>7053452</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2625,7 +2625,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122083879</v>
+        <v>122083869</v>
       </c>
       <c r="B20" t="n">
         <v>57379</v>
@@ -2659,16 +2659,28 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Gåstjärnvalen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>418631</v>
+        <v>418453</v>
       </c>
       <c r="R20" t="n">
-        <v>7053701</v>
+        <v>7053383</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2701,11 +2713,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-01-10</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2732,7 +2739,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122083898</v>
+        <v>122083892</v>
       </c>
       <c r="B21" t="n">
         <v>57379</v>
@@ -2772,10 +2779,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>418731</v>
+        <v>418769</v>
       </c>
       <c r="R21" t="n">
-        <v>7053619</v>
+        <v>7053764</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2839,7 +2846,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122083870</v>
+        <v>122083891</v>
       </c>
       <c r="B22" t="n">
         <v>57379</v>
@@ -2879,10 +2886,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>418476</v>
+        <v>418789</v>
       </c>
       <c r="R22" t="n">
-        <v>7053445</v>
+        <v>7053772</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2919,7 +2926,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2946,7 +2953,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122083885</v>
+        <v>122083874</v>
       </c>
       <c r="B23" t="n">
         <v>57379</v>
@@ -2986,10 +2993,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>418741</v>
+        <v>418592</v>
       </c>
       <c r="R23" t="n">
-        <v>7053893</v>
+        <v>7053670</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3053,7 +3060,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122083892</v>
+        <v>122083897</v>
       </c>
       <c r="B24" t="n">
         <v>57379</v>
@@ -3093,10 +3100,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>418769</v>
+        <v>418829</v>
       </c>
       <c r="R24" t="n">
-        <v>7053764</v>
+        <v>7053675</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3160,7 +3167,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122083871</v>
+        <v>122083868</v>
       </c>
       <c r="B25" t="n">
         <v>57379</v>
@@ -3200,10 +3207,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>418491</v>
+        <v>418309</v>
       </c>
       <c r="R25" t="n">
-        <v>7053452</v>
+        <v>7053279</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3267,7 +3274,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122083878</v>
+        <v>122083890</v>
       </c>
       <c r="B26" t="n">
         <v>57379</v>
@@ -3307,10 +3314,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>418620</v>
+        <v>418789</v>
       </c>
       <c r="R26" t="n">
-        <v>7053685</v>
+        <v>7053838</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3374,10 +3381,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122083886</v>
+        <v>122083904</v>
       </c>
       <c r="B27" t="n">
-        <v>57379</v>
+        <v>78651</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3390,21 +3397,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3414,10 +3421,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>418755</v>
+        <v>418450</v>
       </c>
       <c r="R27" t="n">
-        <v>7053901</v>
+        <v>7053262</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3454,7 +3461,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>riktigt</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3481,7 +3488,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122083883</v>
+        <v>122083902</v>
       </c>
       <c r="B28" t="n">
         <v>57379</v>
@@ -3521,10 +3528,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>418739</v>
+        <v>418725</v>
       </c>
       <c r="R28" t="n">
-        <v>7053883</v>
+        <v>7053592</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3561,7 +3568,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3588,7 +3595,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122083897</v>
+        <v>122083898</v>
       </c>
       <c r="B29" t="n">
         <v>57379</v>
@@ -3628,10 +3635,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>418829</v>
+        <v>418731</v>
       </c>
       <c r="R29" t="n">
-        <v>7053675</v>
+        <v>7053619</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3695,7 +3702,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122083889</v>
+        <v>122083870</v>
       </c>
       <c r="B30" t="n">
         <v>57379</v>
@@ -3735,10 +3742,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>418787</v>
+        <v>418476</v>
       </c>
       <c r="R30" t="n">
-        <v>7053837</v>
+        <v>7053445</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3802,7 +3809,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122083876</v>
+        <v>122083889</v>
       </c>
       <c r="B31" t="n">
         <v>57379</v>
@@ -3842,10 +3849,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>418613</v>
+        <v>418787</v>
       </c>
       <c r="R31" t="n">
-        <v>7053668</v>
+        <v>7053837</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3882,7 +3889,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3909,7 +3916,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122083891</v>
+        <v>122083882</v>
       </c>
       <c r="B32" t="n">
         <v>57379</v>
@@ -3949,10 +3956,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>418789</v>
+        <v>418746</v>
       </c>
       <c r="R32" t="n">
-        <v>7053772</v>
+        <v>7053865</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3989,7 +3996,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4016,7 +4023,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122083896</v>
+        <v>122083886</v>
       </c>
       <c r="B33" t="n">
         <v>57379</v>
@@ -4056,10 +4063,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>418900</v>
+        <v>418755</v>
       </c>
       <c r="R33" t="n">
-        <v>7053621</v>
+        <v>7053901</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4123,7 +4130,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122083868</v>
+        <v>122083895</v>
       </c>
       <c r="B34" t="n">
         <v>57379</v>
@@ -4163,10 +4170,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>418309</v>
+        <v>418939</v>
       </c>
       <c r="R34" t="n">
-        <v>7053279</v>
+        <v>7053794</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4230,7 +4237,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122083869</v>
+        <v>122083893</v>
       </c>
       <c r="B35" t="n">
         <v>57379</v>
@@ -4264,28 +4271,16 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Gåstjärnvalen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>418453</v>
+        <v>418775</v>
       </c>
       <c r="R35" t="n">
-        <v>7053383</v>
+        <v>7053757</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4318,6 +4313,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4344,7 +4344,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122083882</v>
+        <v>122083894</v>
       </c>
       <c r="B36" t="n">
         <v>57379</v>
@@ -4384,10 +4384,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>418746</v>
+        <v>418782</v>
       </c>
       <c r="R36" t="n">
-        <v>7053865</v>
+        <v>7053729</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4424,7 +4424,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4451,7 +4451,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122083899</v>
+        <v>122083881</v>
       </c>
       <c r="B37" t="n">
         <v>57379</v>
@@ -4491,10 +4491,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>418744</v>
+        <v>418710</v>
       </c>
       <c r="R37" t="n">
-        <v>7053595</v>
+        <v>7053790</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 57918-2024 artfynd.xlsx
+++ b/artfynd/A 57918-2024 artfynd.xlsx
@@ -913,7 +913,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122083896</v>
+        <v>122083874</v>
       </c>
       <c r="B4" t="n">
         <v>57379</v>
@@ -931,11 +931,6 @@
       <c r="E4" t="n">
         <v>100109</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -953,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>418900</v>
+        <v>418592</v>
       </c>
       <c r="R4" t="n">
-        <v>7053621</v>
+        <v>7053670</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,7 +1015,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122083887</v>
+        <v>122083893</v>
       </c>
       <c r="B5" t="n">
         <v>57379</v>
@@ -1038,11 +1033,6 @@
       <c r="E5" t="n">
         <v>100109</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1060,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>418757</v>
+        <v>418775</v>
       </c>
       <c r="R5" t="n">
-        <v>7053896</v>
+        <v>7053757</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1127,7 +1117,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122083888</v>
+        <v>122083884</v>
       </c>
       <c r="B6" t="n">
         <v>57379</v>
@@ -1145,11 +1135,6 @@
       <c r="E6" t="n">
         <v>100109</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1167,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>418785</v>
+        <v>418739</v>
       </c>
       <c r="R6" t="n">
-        <v>7053838</v>
+        <v>7053883</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1207,7 +1192,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1234,7 +1219,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122083885</v>
+        <v>122083892</v>
       </c>
       <c r="B7" t="n">
         <v>57379</v>
@@ -1252,11 +1237,6 @@
       <c r="E7" t="n">
         <v>100109</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1274,10 +1254,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>418741</v>
+        <v>418769</v>
       </c>
       <c r="R7" t="n">
-        <v>7053893</v>
+        <v>7053764</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,7 +1294,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1341,7 +1321,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122083877</v>
+        <v>122083885</v>
       </c>
       <c r="B8" t="n">
         <v>57379</v>
@@ -1359,11 +1339,6 @@
       <c r="E8" t="n">
         <v>100109</v>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1381,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>418615</v>
+        <v>418741</v>
       </c>
       <c r="R8" t="n">
-        <v>7053683</v>
+        <v>7053893</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1421,7 +1396,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1448,7 +1423,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122083876</v>
+        <v>122083879</v>
       </c>
       <c r="B9" t="n">
         <v>57379</v>
@@ -1466,11 +1441,6 @@
       <c r="E9" t="n">
         <v>100109</v>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1488,10 +1458,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>418613</v>
+        <v>418631</v>
       </c>
       <c r="R9" t="n">
-        <v>7053668</v>
+        <v>7053701</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1528,7 +1498,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1555,7 +1525,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122083878</v>
+        <v>122083888</v>
       </c>
       <c r="B10" t="n">
         <v>57379</v>
@@ -1573,11 +1543,6 @@
       <c r="E10" t="n">
         <v>100109</v>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1595,10 +1560,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>418620</v>
+        <v>418785</v>
       </c>
       <c r="R10" t="n">
-        <v>7053685</v>
+        <v>7053838</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1635,7 +1600,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1662,7 +1627,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122083884</v>
+        <v>122083891</v>
       </c>
       <c r="B11" t="n">
         <v>57379</v>
@@ -1680,11 +1645,6 @@
       <c r="E11" t="n">
         <v>100109</v>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G11" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1702,10 +1662,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>418739</v>
+        <v>418789</v>
       </c>
       <c r="R11" t="n">
-        <v>7053883</v>
+        <v>7053772</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1742,7 +1702,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1769,7 +1729,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122083875</v>
+        <v>122083897</v>
       </c>
       <c r="B12" t="n">
         <v>57379</v>
@@ -1787,11 +1747,6 @@
       <c r="E12" t="n">
         <v>100109</v>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1809,10 +1764,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>418602</v>
+        <v>418829</v>
       </c>
       <c r="R12" t="n">
-        <v>7053668</v>
+        <v>7053675</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1876,7 +1831,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122083901</v>
+        <v>122083889</v>
       </c>
       <c r="B13" t="n">
         <v>57379</v>
@@ -1894,11 +1849,6 @@
       <c r="E13" t="n">
         <v>100109</v>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G13" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1916,10 +1866,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>418735</v>
+        <v>418787</v>
       </c>
       <c r="R13" t="n">
-        <v>7053591</v>
+        <v>7053837</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1956,7 +1906,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1983,7 +1933,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122083903</v>
+        <v>122083896</v>
       </c>
       <c r="B14" t="n">
         <v>57379</v>
@@ -2001,11 +1951,6 @@
       <c r="E14" t="n">
         <v>100109</v>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G14" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2023,10 +1968,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>418664</v>
+        <v>418900</v>
       </c>
       <c r="R14" t="n">
-        <v>7053400</v>
+        <v>7053621</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2063,7 +2008,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2090,7 +2035,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122083879</v>
+        <v>122083886</v>
       </c>
       <c r="B15" t="n">
         <v>57379</v>
@@ -2108,11 +2053,6 @@
       <c r="E15" t="n">
         <v>100109</v>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2130,10 +2070,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>418631</v>
+        <v>418755</v>
       </c>
       <c r="R15" t="n">
-        <v>7053701</v>
+        <v>7053901</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2170,7 +2110,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2197,10 +2137,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122083880</v>
+        <v>122083904</v>
       </c>
       <c r="B16" t="n">
-        <v>57379</v>
+        <v>78652</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2213,21 +2153,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2237,10 +2172,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>418705</v>
+        <v>418450</v>
       </c>
       <c r="R16" t="n">
-        <v>7053783</v>
+        <v>7053262</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2277,7 +2212,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>riktigt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2304,7 +2239,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122083873</v>
+        <v>122083871</v>
       </c>
       <c r="B17" t="n">
         <v>57379</v>
@@ -2322,11 +2257,6 @@
       <c r="E17" t="n">
         <v>100109</v>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2344,10 +2274,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>418544</v>
+        <v>418491</v>
       </c>
       <c r="R17" t="n">
-        <v>7053546</v>
+        <v>7053452</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2411,7 +2341,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122083899</v>
+        <v>122083877</v>
       </c>
       <c r="B18" t="n">
         <v>57379</v>
@@ -2429,11 +2359,6 @@
       <c r="E18" t="n">
         <v>100109</v>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G18" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2451,10 +2376,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>418744</v>
+        <v>418615</v>
       </c>
       <c r="R18" t="n">
-        <v>7053595</v>
+        <v>7053683</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2518,7 +2443,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122083871</v>
+        <v>122083868</v>
       </c>
       <c r="B19" t="n">
         <v>57379</v>
@@ -2536,11 +2461,6 @@
       <c r="E19" t="n">
         <v>100109</v>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G19" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2558,10 +2478,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>418491</v>
+        <v>418309</v>
       </c>
       <c r="R19" t="n">
-        <v>7053452</v>
+        <v>7053279</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2625,7 +2545,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122083869</v>
+        <v>122083876</v>
       </c>
       <c r="B20" t="n">
         <v>57379</v>
@@ -2643,11 +2563,6 @@
       <c r="E20" t="n">
         <v>100109</v>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G20" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2659,28 +2574,16 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Gåstjärnvalen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>418453</v>
+        <v>418613</v>
       </c>
       <c r="R20" t="n">
-        <v>7053383</v>
+        <v>7053668</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2713,6 +2616,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2739,7 +2647,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122083892</v>
+        <v>122083870</v>
       </c>
       <c r="B21" t="n">
         <v>57379</v>
@@ -2757,11 +2665,6 @@
       <c r="E21" t="n">
         <v>100109</v>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G21" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2779,10 +2682,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>418769</v>
+        <v>418476</v>
       </c>
       <c r="R21" t="n">
-        <v>7053764</v>
+        <v>7053445</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2846,7 +2749,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122083891</v>
+        <v>122083880</v>
       </c>
       <c r="B22" t="n">
         <v>57379</v>
@@ -2864,11 +2767,6 @@
       <c r="E22" t="n">
         <v>100109</v>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G22" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2886,10 +2784,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>418789</v>
+        <v>418705</v>
       </c>
       <c r="R22" t="n">
-        <v>7053772</v>
+        <v>7053783</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2926,7 +2824,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2953,7 +2851,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122083874</v>
+        <v>122083881</v>
       </c>
       <c r="B23" t="n">
         <v>57379</v>
@@ -2971,11 +2869,6 @@
       <c r="E23" t="n">
         <v>100109</v>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G23" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2993,10 +2886,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>418592</v>
+        <v>418710</v>
       </c>
       <c r="R23" t="n">
-        <v>7053670</v>
+        <v>7053790</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3033,7 +2926,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3060,7 +2953,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122083897</v>
+        <v>122083875</v>
       </c>
       <c r="B24" t="n">
         <v>57379</v>
@@ -3078,11 +2971,6 @@
       <c r="E24" t="n">
         <v>100109</v>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G24" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -3100,10 +2988,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>418829</v>
+        <v>418602</v>
       </c>
       <c r="R24" t="n">
-        <v>7053675</v>
+        <v>7053668</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3167,7 +3055,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122083868</v>
+        <v>122083895</v>
       </c>
       <c r="B25" t="n">
         <v>57379</v>
@@ -3185,11 +3073,6 @@
       <c r="E25" t="n">
         <v>100109</v>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G25" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -3207,10 +3090,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>418309</v>
+        <v>418939</v>
       </c>
       <c r="R25" t="n">
-        <v>7053279</v>
+        <v>7053794</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3274,7 +3157,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122083890</v>
+        <v>122083898</v>
       </c>
       <c r="B26" t="n">
         <v>57379</v>
@@ -3292,11 +3175,6 @@
       <c r="E26" t="n">
         <v>100109</v>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G26" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -3314,10 +3192,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>418789</v>
+        <v>418731</v>
       </c>
       <c r="R26" t="n">
-        <v>7053838</v>
+        <v>7053619</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3381,10 +3259,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122083904</v>
+        <v>122083882</v>
       </c>
       <c r="B27" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3397,21 +3275,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3421,10 +3294,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>418450</v>
+        <v>418746</v>
       </c>
       <c r="R27" t="n">
-        <v>7053262</v>
+        <v>7053865</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3461,7 +3334,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>riktigt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3488,7 +3361,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122083902</v>
+        <v>122083878</v>
       </c>
       <c r="B28" t="n">
         <v>57379</v>
@@ -3506,11 +3379,6 @@
       <c r="E28" t="n">
         <v>100109</v>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G28" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -3528,10 +3396,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>418725</v>
+        <v>418620</v>
       </c>
       <c r="R28" t="n">
-        <v>7053592</v>
+        <v>7053685</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3595,7 +3463,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122083898</v>
+        <v>122083903</v>
       </c>
       <c r="B29" t="n">
         <v>57379</v>
@@ -3613,11 +3481,6 @@
       <c r="E29" t="n">
         <v>100109</v>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G29" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -3635,10 +3498,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>418731</v>
+        <v>418664</v>
       </c>
       <c r="R29" t="n">
-        <v>7053619</v>
+        <v>7053400</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3702,7 +3565,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122083870</v>
+        <v>122083899</v>
       </c>
       <c r="B30" t="n">
         <v>57379</v>
@@ -3720,11 +3583,6 @@
       <c r="E30" t="n">
         <v>100109</v>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G30" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -3742,10 +3600,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>418476</v>
+        <v>418744</v>
       </c>
       <c r="R30" t="n">
-        <v>7053445</v>
+        <v>7053595</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3809,7 +3667,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122083889</v>
+        <v>122083869</v>
       </c>
       <c r="B31" t="n">
         <v>57379</v>
@@ -3827,11 +3685,6 @@
       <c r="E31" t="n">
         <v>100109</v>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G31" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -3843,16 +3696,28 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Gåstjärnvalen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>418787</v>
+        <v>418453</v>
       </c>
       <c r="R31" t="n">
-        <v>7053837</v>
+        <v>7053383</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3885,11 +3750,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-01-10</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3916,7 +3776,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122083882</v>
+        <v>122083873</v>
       </c>
       <c r="B32" t="n">
         <v>57379</v>
@@ -3934,11 +3794,6 @@
       <c r="E32" t="n">
         <v>100109</v>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G32" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -3956,10 +3811,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>418746</v>
+        <v>418544</v>
       </c>
       <c r="R32" t="n">
-        <v>7053865</v>
+        <v>7053546</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4023,7 +3878,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122083886</v>
+        <v>122083894</v>
       </c>
       <c r="B33" t="n">
         <v>57379</v>
@@ -4041,11 +3896,6 @@
       <c r="E33" t="n">
         <v>100109</v>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G33" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -4063,10 +3913,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>418755</v>
+        <v>418782</v>
       </c>
       <c r="R33" t="n">
-        <v>7053901</v>
+        <v>7053729</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4130,7 +3980,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122083895</v>
+        <v>122083890</v>
       </c>
       <c r="B34" t="n">
         <v>57379</v>
@@ -4148,11 +3998,6 @@
       <c r="E34" t="n">
         <v>100109</v>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G34" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -4170,10 +4015,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>418939</v>
+        <v>418789</v>
       </c>
       <c r="R34" t="n">
-        <v>7053794</v>
+        <v>7053838</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4237,7 +4082,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122083893</v>
+        <v>122083902</v>
       </c>
       <c r="B35" t="n">
         <v>57379</v>
@@ -4255,11 +4100,6 @@
       <c r="E35" t="n">
         <v>100109</v>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -4277,10 +4117,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>418775</v>
+        <v>418725</v>
       </c>
       <c r="R35" t="n">
-        <v>7053757</v>
+        <v>7053592</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4344,7 +4184,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122083894</v>
+        <v>122083887</v>
       </c>
       <c r="B36" t="n">
         <v>57379</v>
@@ -4362,11 +4202,6 @@
       <c r="E36" t="n">
         <v>100109</v>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G36" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -4384,10 +4219,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>418782</v>
+        <v>418757</v>
       </c>
       <c r="R36" t="n">
-        <v>7053729</v>
+        <v>7053896</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4424,7 +4259,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4451,7 +4286,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122083881</v>
+        <v>122083901</v>
       </c>
       <c r="B37" t="n">
         <v>57379</v>
@@ -4469,11 +4304,6 @@
       <c r="E37" t="n">
         <v>100109</v>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G37" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -4491,10 +4321,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>418710</v>
+        <v>418735</v>
       </c>
       <c r="R37" t="n">
-        <v>7053790</v>
+        <v>7053591</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4531,7 +4361,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 57918-2024 artfynd.xlsx
+++ b/artfynd/A 57918-2024 artfynd.xlsx
@@ -1219,7 +1219,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122083892</v>
+        <v>122083888</v>
       </c>
       <c r="B7" t="n">
         <v>57379</v>
@@ -1254,10 +1254,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>418769</v>
+        <v>418785</v>
       </c>
       <c r="R7" t="n">
-        <v>7053764</v>
+        <v>7053838</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,7 +1321,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122083885</v>
+        <v>122083891</v>
       </c>
       <c r="B8" t="n">
         <v>57379</v>
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>418741</v>
+        <v>418789</v>
       </c>
       <c r="R8" t="n">
-        <v>7053893</v>
+        <v>7053772</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1423,7 +1423,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122083879</v>
+        <v>122083892</v>
       </c>
       <c r="B9" t="n">
         <v>57379</v>
@@ -1458,10 +1458,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>418631</v>
+        <v>418769</v>
       </c>
       <c r="R9" t="n">
-        <v>7053701</v>
+        <v>7053764</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1525,7 +1525,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122083888</v>
+        <v>122083885</v>
       </c>
       <c r="B10" t="n">
         <v>57379</v>
@@ -1560,10 +1560,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>418785</v>
+        <v>418741</v>
       </c>
       <c r="R10" t="n">
-        <v>7053838</v>
+        <v>7053893</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1627,7 +1627,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122083891</v>
+        <v>122083879</v>
       </c>
       <c r="B11" t="n">
         <v>57379</v>
@@ -1662,10 +1662,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>418789</v>
+        <v>418631</v>
       </c>
       <c r="R11" t="n">
-        <v>7053772</v>
+        <v>7053701</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1702,7 +1702,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
